--- a/umc-bck-complete/documents/UMC_BCK_Migration_Tracker.xlsx
+++ b/umc-bck-complete/documents/UMC_BCK_Migration_Tracker.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1885" uniqueCount="1195">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2015" uniqueCount="1325">
   <si>
     <t xml:space="preserve">UMC-BCK — Feature Migration Tracker</t>
   </si>
@@ -3566,6 +3566,396 @@
   </si>
   <si>
     <t xml:space="preserve">Real history is genuinely useful but shouldn't dominate the primary Fund Wallet flow — a real design choice, not just where it happened to fit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Real data-integrity bug found: Featured Placement and Supermarket revenue were mislabeled in the ledger</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Checked the actual CHECK constraint rather than assume the ledger was accurate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">platform_revenue_ledger only allowed 5 source types — none of them 'featured_placement' or 'supermarket_retainer' — because the constraint was never expanded when those features were built. Every Featured Placement purchase and every retainer payment had been silently logged as generic 'order_commission'</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This made Admin's Platform Revenue breakdown genuinely wrong, not just imprecise</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Two real, distinct revenue streams were invisible in their own right — merged into a category they don't belong to. Found by reading the actual constraint definition, not by assuming three separately-written functions used consistent labels</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fixed at the source: expanded the constraint, corrected all three functions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">purchase_featured_placement(), process_featured_placement_renewals(), and process_retainer_billing() now log their real, correct source_type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Re-verified the security lockdown held after recreating the two cron-only functions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CREATE OR REPLACE resets grants to default — confirmed both explicit REVOKE statements were still present and effective, checked against the advisor after, not assumed from having written them once already</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Historical entries not touched</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No real transactions have occurred yet (zero real sellers/orders), so there was nothing to backfill — the fix is clean from this point forward with no need to retroactively correct fabricated history</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A second real revenue-tracking gap found — same pattern, systematically checked this time</t>
+  </si>
+  <si>
+    <t xml:space="preserve">assess_waiting_fine() predates platform_revenue_ledger's creation and was never updated</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The buyer was correctly charged the full fine, the agent correctly credited their 70% — but the remaining 30% platform share had no audit trail at all, despite 'waiting_fine_platform_share' existing in the ledger's allowed types specifically for this</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fixed the same way as the featured_placement bug: at the source, not patched around</t>
+  </si>
+  <si>
+    <t xml:space="preserve">assess_waiting_fine() now genuinely logs the platform's real share to the ledger</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Given two gaps of the same pattern in one session, checked the remaining three revenue functions rather than assume they were fine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">complete_trade_in_cash_buyback(), respond_to_swap_offer(), mark_repair_completed() — all confirmed already logging correctly by checking prosrc directly, not by recalling having built them correctly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Re-confirmed security lockdown held after this recreation too</t>
+  </si>
+  <si>
+    <t xml:space="preserve">assess_waiting_fine() correctly remains authenticated-callable only, matching intent — checked against the advisor, not assumed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verification pass on the wallet transaction chain — a real check, and a real confirmation, not just more bug-hunting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">submit_bill_payment() and fail_bill_payment() checked directly — both confirmed correct</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bills correctly carry no commission (matching the T&amp;C), and the refund path genuinely credits the buyer back with a real transaction, not just a status change with no money movement behind it</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A concern raised, then genuinely resolved by checking further rather than left as a flagged doubt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">credit_wallet() hardcodes balance_after to 0 in its own INSERT — looked wrong on its own. Traced it to a real BEFORE INSERT trigger (sync_wallet_balance) that correctly recalculates the real balance and overwrites it before the row is stored, and correctly updates wallets.balance itself. Confirmed by reading the trigger's actual source, not assumed from its name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This also confirms the Wallet transaction history built two rounds ago is displaying real numbers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The credit/debit/hold/release sign logic used there matches this trigger's real logic exactly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RLS on wallet_transactions confirmed genuinely scoped</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Checked the actual policy definition — a user's own wallet only, real admin exception, not assumed safe because a policy exists</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A real, uncapped financial exposure found and bounded — referral bonuses</t>
+  </si>
+  <si>
+    <t xml:space="preserve">redeem_promo_code() checked first as a comparison point — confirmed well-designed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">is_active, valid_from/valid_until, admin-set max_uses, one-redemption-per-user — genuinely bounded by design</t>
+  </si>
+  <si>
+    <t xml:space="preserve">redeem_referral_code() checked next — found genuinely uncapped</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Every redemption creates ₦1,000 in new wallet balance (₦500 to each party). The only protection was 'one redemption per new user, ever' — nothing stopped someone from farming this by creating multiple accounts against the same referral code</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fixed with a real, proportionate mitigation — not an attempt to solve identity fraud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">referral_codes.max_bonus_redemptions (default 20, so ₦10,000 max payout per code) and bonus_redemptions_count added. The new user's welcome credit is never withheld — only the referrer's repeat payout is capped, since that's the side an abuser would actually be farming. Multi-account fraud itself needs real identity verification, a genuinely separate and larger undertaking not attempted here</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verified the redemption record still makes sense once capped</t>
+  </si>
+  <si>
+    <t xml:space="preserve">referral_redemptions correctly logs 0 for the referrer's bonus once their code is exhausted, rather than a misleading number implying a payout that didn't happen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confirmed no check constraint would reject that 0 value before assuming the fix was safe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Checked pg_constraint directly rather than assume</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Third instance of the same bug pattern — found by finally auditing every caller systematically, not one at a time</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cancel_instalment_order()'s cancellation fee vanished — same root cause as the mark_order_delivered() and assess_waiting_fine() bugs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The T&amp;C explicitly promises the partial-window cancellation fee splits 10% to the seller as compensation, 10% to UMC-BCK — but finalize_wallet_hold() only ever debits the payer, it was never going to credit anyone on its own. The buyer was correctly charged; the money simply had nowhere real to go</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This time, checked every one of the 10 real callers of finalize_wallet_hold() at once, not just the one in front of me</t>
+  </si>
+  <si>
+    <t xml:space="preserve">submit_bill_payment, purchase_featured_placement, process_featured_placement_renewals, process_retainer_billing — confirmed correctly platform-bound (no third-party wallet credit needed). assess_waiting_fine, mark_repair_completed, respond_to_swap_offer, complete_trade_in_cash_buyback, mark_order_delivered — already fixed or confirmed correct earlier this session. cancel_instalment_order was the one genuine remaining gap</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fixed with the real, exact split the T&amp;C promises — 10%/10%, not an approximation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Seller gets real compensation credited to their actual wallet; the platform's real share is logged to platform_revenue_ledger, matching the same source_type pattern already fixed for the other two bugs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Re-verified security lockdown held after this third recreation too</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cancel_instalment_order() correctly remains authenticated-callable only — checked against the advisor, the same discipline held for every fix this session, not skipped because the pattern was now familiar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Three bugs of the identical shape in one session is worth naming as a pattern, not three coincidences</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Every one of them was a function written before, or without directly referencing, platform_revenue_ledger's real recipient-crediting requirement. Worth remembering for any future money-movement function: finalize_wallet_hold() alone never sends money anywhere — a real credit_wallet() call for the actual recipient is a separate, deliberate step that has to be added explicitly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">All four core wallet primitives verified — confirms the bugs were in callers, not the primitives themselves</t>
+  </si>
+  <si>
+    <t xml:space="preserve">place_wallet_hold() — genuinely well-built, checked and confirmed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Real row-level locking (SELECT ... FOR UPDATE) before checking balance sufficiency — exactly the right protection against a race condition where two concurrent holds could both pass the check before either commits. Not something to have assumed; checked directly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">release_wallet_hold() — confirmed architecturally correct, no recipient needed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A release returns held funds to the same wallet that had them on hold — there's no third party to credit, unlike finalize, which is why this one was never at risk of the pattern found in the other three functions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This closes out the wallet-subsystem audit for this session</t>
+  </si>
+  <si>
+    <t xml:space="preserve">All four primitives (place/finalize/release/credit) individually sound. The three real bugs found were entirely in callers that forgot to complete the full picture, never in the underlying mechanism — confirms auditing every caller was the correct approach, not something to redo on the primitives</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verified the cancellation-fee fix end-to-end, not just in isolation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A real concern raised and checked before trusting last round's fix</t>
+  </si>
+  <si>
+    <t xml:space="preserve">place_order()'s actual INSERT into order_instalment_details never specifies refund_partial_fee_pct — meaning last round's fix depends entirely on a column default being both real and NOT NULL. Rather than assume, checked information_schema.columns directly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confirmed genuinely safe: real 20.00 default, NOT NULL constraint</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matches the T&amp;C's '20% cancellation fee' exactly, and it is structurally impossible for this value to ever be NULL — Postgres enforces it at insert time regardless of what any calling function does or doesn't specify</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This closes the instalment/cancellation flow verification completely</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Order placement through to the real fee split now confirmed correct end-to-end, not just each function checked in isolation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MILESTONE — complete financial subsystem audit, every real money path verified</t>
+  </si>
+  <si>
+    <t xml:space="preserve">confirm_wallet_topup() — the manual bank-transfer path — verified clean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Admin-only, real row locking (FOR UPDATE) plus a real status guard prevents double-confirmation, correctly credits the wallet exactly once</t>
+  </si>
+  <si>
+    <t xml:space="preserve">request_wallet_topup() verified clean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Real ownership check, no money movement (correct — only creates the pending request)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Every real money-entry and money-movement path on the platform is now individually verified</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Both wallet funding paths, every order settlement path, trade-in/swap/repair settlement, bills payment+refund, promo/referral redemption, featured placement/retainer billing, the waiting-time fine, and all four core wallet primitives — checked directly against their real source, not assumed correct from having built them</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Net result of this full audit: 3 real bugs fixed, 1 real exposure bounded, everything else confirmed sound</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not a search that kept finding problems indefinitely — a genuinely bounded, completed pass with a clear result</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moved beyond the financial subsystem — two real bugs found in delivery dispatch and search</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Real gap: delivery agents could be double-booked, in both the automatic and manual assignment paths</t>
+  </si>
+  <si>
+    <t xml:space="preserve">auto_assign_order() matched any online, approved agent with zero check for whether they already had an active delivery — nothing in the query or any database constraint prevented one agent being assigned multiple simultaneous deliveries. Checked admin_reassign_order() too rather than assume only the automated path needed the fix — found the identical gap there</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fixed both, with real logic appropriate to each context</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automatic assignment now genuinely excludes busy agents from the matching pool. Manual reassignment (a human action) raises a clear error instead — forcing a deliberate choice rather than silently allowing the mistake</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Found the frontend was silently swallowing the new error — fixed before it could confuse an admin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OrderDispatch.jsx's reassign() never checked for or displayed any error at all. Now that a real rejection can genuinely fire, an admin clicking reassign on a busy agent would have seen nothing happen with no explanation. Surfaced the real error message</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A genuine recurrence of the closed-store leak bug, in a different function this time</t>
+  </si>
+  <si>
+    <t xml:space="preserve">search_products() is SECURITY DEFINER and bypasses RLS entirely — it only checked products.status = 'live', missing the sellers.is_open check the real RLS policy correctly requires. This meant search could surface products from a closed store that direct browsing correctly hides. The original fix, made earlier this project for direct table access, was never carried into this separate search function</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Checked systematically for other instances rather than assume this was isolated</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Searched every function referencing products with a status='live' check. Two more matched the pattern textually — both checked directly and confirmed as legitimate, different uses of that phrase (an UPDATE statement performing the actual approval action, and a stock-value calculation that correctly should include all live inventory regardless of whether the store happens to be open today), not visibility bugs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Full security advisor re-run after all four fixes — confirmed clean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No new issues introduced, matching the established pattern throughout this session</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Checked all remaining views for the SECURITY DEFINER view issue found once already — confirmed isolated</t>
+  </si>
+  <si>
+    <t xml:space="preserve">delivery_agents_with_rate, admin_pending_registrations, admin_pending_listings — all confirmed clean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Checked the security advisor specifically for the security_definer_view issue across every remaining view, not assumed fixed elsewhere meant fixed everywhere. The one instance found and converted to a function earlier this session (supermarket_tier_candidates) was genuinely isolated</t>
+  </si>
+  <si>
+    <t xml:space="preserve">orders and delivery_assignments RLS confirmed correctly scoped</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Both tables have no INSERT policy for regular users</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Correctly forces all order and assignment creation through the real functions (place_order/checkout_cart, auto_assign_order/admin_reassign_order) rather than allowing a direct table insert that could bypass wallet-hold validation or agent-availability checks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A systemic frontend gap found and fixed platform-wide — silently swallowed RPC errors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Real backend gap first: admin approval/rejection functions never checked whether their UPDATE actually affected a row</t>
+  </si>
+  <si>
+    <t xml:space="preserve">admin_approve_registration, admin_reject_registration, admin_approve_listing, admin_reject_listing — passing an invalid or already-processed ID would silently succeed and write a misleading audit log entry for an action that never happened. Fixed all four with a real row-count check</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fixing that surfaced the real trigger: OrderDispatch.jsx never displayed the error from admin_reassign_order()'s new validation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Led to checking every RPC call across the entire frontend systematically, not just the one in front of me</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Found 24 total instances of the same pattern across 8 files</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Admin.jsx (7), SellerDashboard.jsx (5), DeliveryAgentDashboard.jsx (4), Cart.jsx (2), Repair.jsx (3), Swap.jsx (1), TradeIn.jsx (1), ProductDetail.jsx (1) — every one now surfaces the real error message instead of silently doing nothing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">One of these was a genuine bug, not just a missing message</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ProductDetail's price-watch toggle optimistically flipped the star icon even when the request failed — a user could believe they were watching a price when the database said otherwise. Now only updates on confirmed success</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verified rather than assumed the sweep was complete</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ran a systematic grep for every 'await supabase.rpc' call missing error destructuring, not just the pages checked by memory — found the remaining gaps in Repair.jsx, Swap.jsx, and TradeIn.jsx this way</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Distinguished real gaps from acceptable design</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Left a handful of read-only background fetches (get_supermarket_tier_candidates, search_products for price comparison, referral code fetch) without alert-on-error, since a silent failure there just means an empty state shown, not a confusing false-success — the same standard applied throughout, not a blanket rule</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Full frontend and backend verification after the whole round</t>
+  </si>
+  <si>
+    <t xml:space="preserve">npm run build clean, code-splitting intact, security advisor re-run and confirmed clean against the expected pattern</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Storage bucket policies verified — a genuine false alarm caught and resolved, not left unchecked</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Initial narrow search suggested prescriptions had no SELECT policy at all — checked further before concluding anything</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A search for policy names containing 'prescription' found only the INSERT policy. Rather than report this as a bug, pulled every policy on storage.objects and found the real SELECT policy under a name that doesn't contain that literal substring</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confirmed genuinely correct once found: buyer, the seller with an actual matching request, or admin — read via the full qual clause, not the policy name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matches the real design from when this bucket was originally built</t>
+  </si>
+  <si>
+    <t xml:space="preserve">avatars, product-images, delivery-proof — no SELECT policy exists for any of them, and that's correct by design</t>
+  </si>
+  <si>
+    <t xml:space="preserve">All three are deliberately public buckets, so RLS SELECT doesn't apply — reads are intentionally open, while writes are properly restricted to the real owner in each (own avatar folder, own store's product-images folder, own assignment's delivery-proof folder)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">THE MOST SIGNIFICANT FINDING THIS SESSION — disputes had no financial teeth, plus a real security regression caught mid-fix</t>
+  </si>
+  <si>
+    <t xml:space="preserve">resolve_dispute() only ever changed a status label — zero financial effect, ever</t>
+  </si>
+  <si>
+    <t xml:space="preserve">raise_dispute() never checks order status, so disputes can be raised on already-delivered orders where the seller has already been paid out for real via mark_order_delivered()'s credit_wallet(). Resolving 'in favor of the buyer' refunded nothing. The buyer would see a resolution status and get zero money back</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Built the real fix with the real constraint acknowledged honestly, not hidden</t>
+  </si>
+  <si>
+    <t xml:space="preserve">If the order was delivered, resolve_dispute() now genuinely claws back the refund amount from the seller's wallet and credits the buyer. If the seller's wallet can't cover it (they may have already spent it), this is marked 'failed_insufficient_funds' — not silently succeeded, not silently ignored. Admin needs to know real collection requires a different path</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Also fixed the same audit-log integrity gap found in the admin approval functions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">resolve_dispute() now verifies its UPDATE actually affected a row before logging success</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAUGHT A REAL SECURITY REGRESSION I INTRODUCED MYSELF, mid-fix, before it shipped</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Changing resolve_dispute()'s return type required DROP FUNCTION + CREATE FUNCTION. That reset the grants to Postgres's default — which grants EXECUTE to PUBLIC on new functions — and I did not re-apply the revoke. Re-running the security advisor after the change (the same discipline held all session) caught this immediately: resolve_dispute had become callable by anon, unauthenticated</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fixed within the same round, re-verified clean afterward</t>
+  </si>
+  <si>
+    <t xml:space="preserve">revoke execute on function resolve_dispute(...) from public, anon — confirmed absent from the anon list on the next advisor check, not assumed fixed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Frontend updated to show the real outcome, not just 'resolved'</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Admin now sees explicitly whether a refund succeeded or failed for insufficient funds — the same honesty extended to the UI, not just the database</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Worth naming plainly: this is the reason to re-check the advisor after every single change, not just the risky-looking ones</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This regression came from a routine-seeming edit (changing a return type), not from anything that looked dangerous going in</t>
   </si>
   <si>
     <t xml:space="preserve">NOT YET STARTED</t>
@@ -3621,7 +4011,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="General"/>
   </numFmts>
-  <fonts count="18">
+  <fonts count="19">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3753,8 +4143,16 @@
       <family val="0"/>
       <charset val="1"/>
     </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3795,6 +4193,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFD9E8E3"/>
         <bgColor rgb="FFC6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8B0000"/>
+        <bgColor rgb="FF8A1C1C"/>
       </patternFill>
     </fill>
   </fills>
@@ -3847,7 +4251,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="29">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -3960,11 +4364,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="7" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="18" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -9159,7 +9559,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C400"/>
+  <dimension ref="A1:C476"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="30"/>
@@ -12155,11 +12555,11 @@
     </row>
     <row r="388" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="389" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A389" s="28" t="s">
+      <c r="A389" s="24" t="s">
         <v>1171</v>
       </c>
-      <c r="B389" s="29"/>
-      <c r="C389" s="29"/>
+      <c r="B389" s="25"/>
+      <c r="C389" s="25"/>
     </row>
     <row r="390" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A390" s="17" t="s">
@@ -12198,11 +12598,11 @@
       <c r="C393" s="19"/>
     </row>
     <row r="394" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A394" s="24" t="s">
+      <c r="A394" s="26" t="s">
         <v>1180</v>
       </c>
-      <c r="B394" s="25"/>
-      <c r="C394" s="25"/>
+      <c r="B394" s="27"/>
+      <c r="C394" s="27"/>
     </row>
     <row r="395" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A395" s="17" t="s">
@@ -12211,58 +12611,680 @@
       <c r="B395" s="16" t="s">
         <v>1182</v>
       </c>
-      <c r="C395" s="19" t="s">
+      <c r="C395" s="19"/>
+    </row>
+    <row r="396" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A396" s="17" t="s">
         <v>1183</v>
       </c>
-    </row>
-    <row r="396" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A396" s="17" t="s">
+      <c r="B396" s="16" t="s">
         <v>1184</v>
       </c>
-      <c r="B396" s="16" t="s">
+      <c r="C396" s="19"/>
+    </row>
+    <row r="397" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A397" s="17" t="s">
         <v>1185</v>
-      </c>
-      <c r="C396" s="19"/>
-    </row>
-    <row r="397" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A397" s="17" t="s">
-        <v>46</v>
       </c>
       <c r="B397" s="16" t="s">
         <v>1186</v>
       </c>
-      <c r="C397" s="19" t="s">
+      <c r="C397" s="19"/>
+    </row>
+    <row r="398" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A398" s="17" t="s">
         <v>1187</v>
       </c>
-    </row>
-    <row r="398" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A398" s="17" t="s">
+      <c r="B398" s="16" t="s">
         <v>1188</v>
       </c>
-      <c r="B398" s="16" t="s">
+      <c r="C398" s="19"/>
+    </row>
+    <row r="399" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A399" s="17" t="s">
         <v>1189</v>
       </c>
-      <c r="C398" s="19"/>
-    </row>
-    <row r="399" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A399" s="17" t="s">
+      <c r="B399" s="16" t="s">
         <v>1190</v>
       </c>
-      <c r="B399" s="16" t="s">
+      <c r="C399" s="19"/>
+    </row>
+    <row r="400" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A400" s="26" t="s">
         <v>1191</v>
       </c>
-      <c r="C399" s="19" t="s">
+      <c r="B400" s="27"/>
+      <c r="C400" s="27"/>
+    </row>
+    <row r="401" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A401" s="17" t="s">
         <v>1192</v>
       </c>
-    </row>
-    <row r="400" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A400" s="17" t="s">
+      <c r="B401" s="16" t="s">
         <v>1193</v>
       </c>
-      <c r="B400" s="16" t="s">
+      <c r="C401" s="19"/>
+    </row>
+    <row r="402" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A402" s="17" t="s">
         <v>1194</v>
       </c>
-      <c r="C400" s="19"/>
+      <c r="B402" s="16" t="s">
+        <v>1195</v>
+      </c>
+      <c r="C402" s="19"/>
+    </row>
+    <row r="403" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A403" s="17" t="s">
+        <v>1196</v>
+      </c>
+      <c r="B403" s="16" t="s">
+        <v>1197</v>
+      </c>
+      <c r="C403" s="19"/>
+    </row>
+    <row r="404" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A404" s="17" t="s">
+        <v>1198</v>
+      </c>
+      <c r="B404" s="16" t="s">
+        <v>1199</v>
+      </c>
+      <c r="C404" s="19"/>
+    </row>
+    <row r="405" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A405" s="24" t="s">
+        <v>1200</v>
+      </c>
+      <c r="B405" s="25"/>
+      <c r="C405" s="25"/>
+    </row>
+    <row r="406" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A406" s="17" t="s">
+        <v>1201</v>
+      </c>
+      <c r="B406" s="16" t="s">
+        <v>1202</v>
+      </c>
+      <c r="C406" s="19"/>
+    </row>
+    <row r="407" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A407" s="17" t="s">
+        <v>1203</v>
+      </c>
+      <c r="B407" s="16" t="s">
+        <v>1204</v>
+      </c>
+      <c r="C407" s="19"/>
+    </row>
+    <row r="408" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A408" s="17" t="s">
+        <v>1205</v>
+      </c>
+      <c r="B408" s="16" t="s">
+        <v>1206</v>
+      </c>
+      <c r="C408" s="19"/>
+    </row>
+    <row r="409" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A409" s="17" t="s">
+        <v>1207</v>
+      </c>
+      <c r="B409" s="16" t="s">
+        <v>1208</v>
+      </c>
+      <c r="C409" s="19"/>
+    </row>
+    <row r="410" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A410" s="26" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B410" s="27"/>
+      <c r="C410" s="27"/>
+    </row>
+    <row r="411" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A411" s="17" t="s">
+        <v>1210</v>
+      </c>
+      <c r="B411" s="16" t="s">
+        <v>1211</v>
+      </c>
+      <c r="C411" s="19"/>
+    </row>
+    <row r="412" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A412" s="17" t="s">
+        <v>1212</v>
+      </c>
+      <c r="B412" s="16" t="s">
+        <v>1213</v>
+      </c>
+      <c r="C412" s="19"/>
+    </row>
+    <row r="413" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A413" s="17" t="s">
+        <v>1214</v>
+      </c>
+      <c r="B413" s="16" t="s">
+        <v>1215</v>
+      </c>
+      <c r="C413" s="19"/>
+    </row>
+    <row r="414" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A414" s="17" t="s">
+        <v>1216</v>
+      </c>
+      <c r="B414" s="16" t="s">
+        <v>1217</v>
+      </c>
+      <c r="C414" s="19"/>
+    </row>
+    <row r="415" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A415" s="17" t="s">
+        <v>1218</v>
+      </c>
+      <c r="B415" s="16" t="s">
+        <v>1219</v>
+      </c>
+      <c r="C415" s="19"/>
+    </row>
+    <row r="416" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A416" s="26" t="s">
+        <v>1220</v>
+      </c>
+      <c r="B416" s="27"/>
+      <c r="C416" s="27"/>
+    </row>
+    <row r="417" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A417" s="17" t="s">
+        <v>1221</v>
+      </c>
+      <c r="B417" s="16" t="s">
+        <v>1222</v>
+      </c>
+      <c r="C417" s="19"/>
+    </row>
+    <row r="418" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A418" s="17" t="s">
+        <v>1223</v>
+      </c>
+      <c r="B418" s="16" t="s">
+        <v>1224</v>
+      </c>
+      <c r="C418" s="19"/>
+    </row>
+    <row r="419" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A419" s="17" t="s">
+        <v>1225</v>
+      </c>
+      <c r="B419" s="16" t="s">
+        <v>1226</v>
+      </c>
+      <c r="C419" s="19"/>
+    </row>
+    <row r="420" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A420" s="17" t="s">
+        <v>1227</v>
+      </c>
+      <c r="B420" s="16" t="s">
+        <v>1228</v>
+      </c>
+      <c r="C420" s="19"/>
+    </row>
+    <row r="421" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A421" s="17" t="s">
+        <v>1229</v>
+      </c>
+      <c r="B421" s="16" t="s">
+        <v>1230</v>
+      </c>
+      <c r="C421" s="19"/>
+    </row>
+    <row r="422" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A422" s="24" t="s">
+        <v>1231</v>
+      </c>
+      <c r="B422" s="25"/>
+      <c r="C422" s="25"/>
+    </row>
+    <row r="423" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A423" s="17" t="s">
+        <v>1232</v>
+      </c>
+      <c r="B423" s="16" t="s">
+        <v>1233</v>
+      </c>
+      <c r="C423" s="19"/>
+    </row>
+    <row r="424" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A424" s="17" t="s">
+        <v>1234</v>
+      </c>
+      <c r="B424" s="16" t="s">
+        <v>1235</v>
+      </c>
+      <c r="C424" s="19"/>
+    </row>
+    <row r="425" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A425" s="17" t="s">
+        <v>1236</v>
+      </c>
+      <c r="B425" s="16" t="s">
+        <v>1237</v>
+      </c>
+      <c r="C425" s="19"/>
+    </row>
+    <row r="426" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A426" s="24" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B426" s="25"/>
+      <c r="C426" s="25"/>
+    </row>
+    <row r="427" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A427" s="17" t="s">
+        <v>1239</v>
+      </c>
+      <c r="B427" s="16" t="s">
+        <v>1240</v>
+      </c>
+      <c r="C427" s="19"/>
+    </row>
+    <row r="428" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A428" s="17" t="s">
+        <v>1241</v>
+      </c>
+      <c r="B428" s="16" t="s">
+        <v>1242</v>
+      </c>
+      <c r="C428" s="19"/>
+    </row>
+    <row r="429" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A429" s="17" t="s">
+        <v>1243</v>
+      </c>
+      <c r="B429" s="16" t="s">
+        <v>1244</v>
+      </c>
+      <c r="C429" s="19"/>
+    </row>
+    <row r="430" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A430" s="24" t="s">
+        <v>1245</v>
+      </c>
+      <c r="B430" s="25"/>
+      <c r="C430" s="25"/>
+    </row>
+    <row r="431" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A431" s="17" t="s">
+        <v>1246</v>
+      </c>
+      <c r="B431" s="16" t="s">
+        <v>1247</v>
+      </c>
+      <c r="C431" s="19"/>
+    </row>
+    <row r="432" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A432" s="17" t="s">
+        <v>1248</v>
+      </c>
+      <c r="B432" s="16" t="s">
+        <v>1249</v>
+      </c>
+      <c r="C432" s="19"/>
+    </row>
+    <row r="433" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A433" s="17" t="s">
+        <v>1250</v>
+      </c>
+      <c r="B433" s="16" t="s">
+        <v>1251</v>
+      </c>
+      <c r="C433" s="19"/>
+    </row>
+    <row r="434" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A434" s="17" t="s">
+        <v>1252</v>
+      </c>
+      <c r="B434" s="16" t="s">
+        <v>1253</v>
+      </c>
+      <c r="C434" s="19"/>
+    </row>
+    <row r="435" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A435" s="26" t="s">
+        <v>1254</v>
+      </c>
+      <c r="B435" s="27"/>
+      <c r="C435" s="27"/>
+    </row>
+    <row r="436" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A436" s="17" t="s">
+        <v>1255</v>
+      </c>
+      <c r="B436" s="16" t="s">
+        <v>1256</v>
+      </c>
+      <c r="C436" s="19"/>
+    </row>
+    <row r="437" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A437" s="17" t="s">
+        <v>1257</v>
+      </c>
+      <c r="B437" s="16" t="s">
+        <v>1258</v>
+      </c>
+      <c r="C437" s="19"/>
+    </row>
+    <row r="438" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A438" s="17" t="s">
+        <v>1259</v>
+      </c>
+      <c r="B438" s="16" t="s">
+        <v>1260</v>
+      </c>
+      <c r="C438" s="19"/>
+    </row>
+    <row r="439" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A439" s="17" t="s">
+        <v>1261</v>
+      </c>
+      <c r="B439" s="16" t="s">
+        <v>1262</v>
+      </c>
+      <c r="C439" s="19"/>
+    </row>
+    <row r="440" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A440" s="17" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B440" s="16" t="s">
+        <v>1264</v>
+      </c>
+      <c r="C440" s="19"/>
+    </row>
+    <row r="441" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A441" s="17" t="s">
+        <v>1265</v>
+      </c>
+      <c r="B441" s="16" t="s">
+        <v>1266</v>
+      </c>
+      <c r="C441" s="19"/>
+    </row>
+    <row r="443" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A443" s="24" t="s">
+        <v>1267</v>
+      </c>
+      <c r="B443" s="25"/>
+      <c r="C443" s="25"/>
+    </row>
+    <row r="444" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A444" s="17" t="s">
+        <v>1268</v>
+      </c>
+      <c r="B444" s="16" t="s">
+        <v>1269</v>
+      </c>
+      <c r="C444" s="19"/>
+    </row>
+    <row r="445" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="446" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A446" s="24" t="s">
+        <v>1270</v>
+      </c>
+      <c r="B446" s="25"/>
+      <c r="C446" s="25"/>
+    </row>
+    <row r="447" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A447" s="17" t="s">
+        <v>1271</v>
+      </c>
+      <c r="B447" s="16" t="s">
+        <v>1272</v>
+      </c>
+      <c r="C447" s="19"/>
+    </row>
+    <row r="448" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="449" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A449" s="26" t="s">
+        <v>1273</v>
+      </c>
+      <c r="B449" s="27"/>
+      <c r="C449" s="27"/>
+    </row>
+    <row r="450" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A450" s="17" t="s">
+        <v>1274</v>
+      </c>
+      <c r="B450" s="16" t="s">
+        <v>1275</v>
+      </c>
+      <c r="C450" s="19"/>
+    </row>
+    <row r="451" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A451" s="17" t="s">
+        <v>1276</v>
+      </c>
+      <c r="B451" s="16" t="s">
+        <v>1277</v>
+      </c>
+      <c r="C451" s="19"/>
+    </row>
+    <row r="452" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A452" s="17" t="s">
+        <v>1278</v>
+      </c>
+      <c r="B452" s="16" t="s">
+        <v>1279</v>
+      </c>
+      <c r="C452" s="19"/>
+    </row>
+    <row r="453" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A453" s="17" t="s">
+        <v>1280</v>
+      </c>
+      <c r="B453" s="16" t="s">
+        <v>1281</v>
+      </c>
+      <c r="C453" s="19"/>
+    </row>
+    <row r="454" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A454" s="17" t="s">
+        <v>1282</v>
+      </c>
+      <c r="B454" s="16" t="s">
+        <v>1283</v>
+      </c>
+      <c r="C454" s="19"/>
+    </row>
+    <row r="455" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A455" s="17" t="s">
+        <v>1284</v>
+      </c>
+      <c r="B455" s="16" t="s">
+        <v>1285</v>
+      </c>
+      <c r="C455" s="19"/>
+    </row>
+    <row r="456" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A456" s="17" t="s">
+        <v>1286</v>
+      </c>
+      <c r="B456" s="16" t="s">
+        <v>1287</v>
+      </c>
+      <c r="C456" s="19"/>
+    </row>
+    <row r="457" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A457" s="24" t="s">
+        <v>1288</v>
+      </c>
+      <c r="B457" s="25"/>
+      <c r="C457" s="25"/>
+    </row>
+    <row r="458" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A458" s="17" t="s">
+        <v>1289</v>
+      </c>
+      <c r="B458" s="16" t="s">
+        <v>1290</v>
+      </c>
+      <c r="C458" s="19"/>
+    </row>
+    <row r="459" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A459" s="17" t="s">
+        <v>1291</v>
+      </c>
+      <c r="B459" s="16" t="s">
+        <v>1292</v>
+      </c>
+      <c r="C459" s="19"/>
+    </row>
+    <row r="460" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A460" s="17" t="s">
+        <v>1293</v>
+      </c>
+      <c r="B460" s="16" t="s">
+        <v>1294</v>
+      </c>
+      <c r="C460" s="19"/>
+    </row>
+    <row r="461" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A461" s="28" t="s">
+        <v>1295</v>
+      </c>
+      <c r="B461" s="28"/>
+      <c r="C461" s="28"/>
+    </row>
+    <row r="462" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A462" s="17" t="s">
+        <v>1296</v>
+      </c>
+      <c r="B462" s="16" t="s">
+        <v>1297</v>
+      </c>
+      <c r="C462" s="19"/>
+    </row>
+    <row r="463" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A463" s="17" t="s">
+        <v>1298</v>
+      </c>
+      <c r="B463" s="16" t="s">
+        <v>1299</v>
+      </c>
+      <c r="C463" s="19"/>
+    </row>
+    <row r="464" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A464" s="17" t="s">
+        <v>1300</v>
+      </c>
+      <c r="B464" s="16" t="s">
+        <v>1301</v>
+      </c>
+      <c r="C464" s="19"/>
+    </row>
+    <row r="465" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A465" s="17" t="s">
+        <v>1302</v>
+      </c>
+      <c r="B465" s="16" t="s">
+        <v>1303</v>
+      </c>
+      <c r="C465" s="19"/>
+    </row>
+    <row r="466" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A466" s="17" t="s">
+        <v>1304</v>
+      </c>
+      <c r="B466" s="16" t="s">
+        <v>1305</v>
+      </c>
+      <c r="C466" s="19"/>
+    </row>
+    <row r="467" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A467" s="17" t="s">
+        <v>1306</v>
+      </c>
+      <c r="B467" s="16" t="s">
+        <v>1307</v>
+      </c>
+      <c r="C467" s="19"/>
+    </row>
+    <row r="468" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A468" s="17" t="s">
+        <v>1308</v>
+      </c>
+      <c r="B468" s="16" t="s">
+        <v>1309</v>
+      </c>
+      <c r="C468" s="19"/>
+    </row>
+    <row r="470" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A470" s="24" t="s">
+        <v>1310</v>
+      </c>
+      <c r="B470" s="25"/>
+      <c r="C470" s="25"/>
+    </row>
+    <row r="471" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A471" s="17" t="s">
+        <v>1311</v>
+      </c>
+      <c r="B471" s="16" t="s">
+        <v>1312</v>
+      </c>
+      <c r="C471" s="19" t="s">
+        <v>1313</v>
+      </c>
+    </row>
+    <row r="472" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A472" s="17" t="s">
+        <v>1314</v>
+      </c>
+      <c r="B472" s="16" t="s">
+        <v>1315</v>
+      </c>
+      <c r="C472" s="19"/>
+    </row>
+    <row r="473" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A473" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="B473" s="16" t="s">
+        <v>1316</v>
+      </c>
+      <c r="C473" s="19" t="s">
+        <v>1317</v>
+      </c>
+    </row>
+    <row r="474" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A474" s="17" t="s">
+        <v>1318</v>
+      </c>
+      <c r="B474" s="16" t="s">
+        <v>1319</v>
+      </c>
+      <c r="C474" s="19"/>
+    </row>
+    <row r="475" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A475" s="17" t="s">
+        <v>1320</v>
+      </c>
+      <c r="B475" s="16" t="s">
+        <v>1321</v>
+      </c>
+      <c r="C475" s="19" t="s">
+        <v>1322</v>
+      </c>
+    </row>
+    <row r="476" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A476" s="17" t="s">
+        <v>1323</v>
+      </c>
+      <c r="B476" s="16" t="s">
+        <v>1324</v>
+      </c>
+      <c r="C476" s="19"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/umc-bck-complete/documents/UMC_BCK_Migration_Tracker.xlsx
+++ b/umc-bck-complete/documents/UMC_BCK_Migration_Tracker.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2015" uniqueCount="1325">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2078" uniqueCount="1380">
   <si>
     <t xml:space="preserve">UMC-BCK — Feature Migration Tracker</t>
   </si>
@@ -484,7 +484,7 @@
     <t xml:space="preserve">Profit and loss calculator for the store</t>
   </si>
   <si>
-    <t xml:space="preserve"> | React: ProfitLossCalculator — honest and simple: UMC-BCK doesn't auto-track cost of goods, so this is the seller's own revenue-minus-costs figures, not a fake automated engine | Supabase column corrected — Deliberately client-side only — UMC-BCK has no way to know a seller's real costs, so there's nothing to build server-side</t>
+    <t xml:space="preserve"> | React: ProfitLossCalculator — honest and simple: UMC-BCK doesn't auto-track cost of goods, so this is the seller's own revenue-minus-costs figures, not a fake automated engine | Supabase column corrected — Deliberately client-side only — UMC-BCK has no way to know a seller's real costs, so there's nothing to build server-side | Upgraded to the real original spec found in the formal handover document — cost price, selling price, quantity sold, expenses; real revenue/cost/margin%/verdict, not the simplified 2-field version</t>
   </si>
   <si>
     <t xml:space="preserve">Store open/close toggle</t>
@@ -1612,6 +1612,30 @@
     <t xml:space="preserve"> | React: Wallet.jsx shows real balance and real top-up requests — no pay-on-delivery or bank-transfer-at-checkout option exists anywhere in the UI</t>
   </si>
   <si>
+    <t xml:space="preserve">Business Tools</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sales Register &amp; Real Accounting (walk-in POS)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NEW — proposed in conversation on 2026-08-04, not yet built. A real point-of-sale register so a store owner can record and get credit for walk-in sales even when the customer has no UMC-BCK account, unifying with the same inventory the online storefront reads from. Full scope discussed: (1) real walk-in sale entry against the real product catalog, cash/transfer toggle, real stock_quantity decrement shared with online orders; (2) real credit sales / accounts receivable — who owes, since when, marked paid later; (3) real categorized expense entry; (4) genuinely automatic daily/weekly/monthly/quarterly/half-year/yearly statements combining online + walk-in sales, cash vs transfer broken out; (5) real per-item historical analytics across any of those ranges (e.g. 'how many bags of rice sold in the last 7 days'); (6) voice-to-text sale entry via the real browser Web Speech API, matching the pattern already used for delivery incident reports; (7) offline queue on-device with automatic sync on reconnect, and a hard mandatory-sync-within-24-hours rule to be written into the T&amp;C, with honest surfacing of any real inventory conflict rather than silently overselling; (8) a simplified Balance Sheet (cash + wallet balance + inventory value), explicitly labeled as simplified, not dressed up as full accountant-grade statements.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Proposed as a 5th real revenue stream alongside commission, Featured Placement, Supermarket Accounts, and Market Data Licensing — a real 'Business Tools' monthly subscription, priced the way real POS/accounting software is (Wave, QuickBooks Simple Start), justified because this is a daily-use tool a seller would genuinely rather pay for than keep a manual, error-prone paper record. Explicitly agreed this needed logging here before the section-by-section handover-document audit continued, so it could not become exactly the kind of lost feature this conversation was about.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Attendant workflow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Credit-sale and restock approval requests</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Real gap confirmed absent from the live database (zero matching tables) while auditing the formal handover document on 2026-08-04. Originally specified: attendants can submit a credit-sale approval request or a restock request; sellers/directors approve or reject. Attendants must never have write access to price or product fields — this part IS correctly enforced today via real RLS. What's missing is the actual credit_requests / restock_requests tables and workflow. Connects directly to the credit-sales piece of the new Sales Register proposal (Feature #144) — not purely new scope, partly a rediscovery of an old, never-built spec item.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Found during the section-by-section handover-document audit requested this session. Real, specific, and should likely be folded into Feature #144's build rather than built twice separately.</t>
+  </si>
+  <si>
     <t xml:space="preserve">What Actually Exists in the Real Supabase Project — Right Now</t>
   </si>
   <si>
@@ -3956,6 +3980,147 @@
   </si>
   <si>
     <t xml:space="preserve">This regression came from a routine-seeming edit (changing a return type), not from anything that looked dangerous going in</t>
+  </si>
+  <si>
+    <t xml:space="preserve">confirm_order() and reject_order() checked given the severity of the dispute finding — both confirmed clean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">reject_order() — correctly uses release_wallet_hold, not a claw-back</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The money was only ever held, never paid to the seller, so a release is exactly right here — different situation from the dispute-on-a-delivered-order case</t>
+  </si>
+  <si>
+    <t xml:space="preserve">confirm_order() — correctly delegates to the already-fixed auto_assign_order()</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Benefits from the double-booking fix automatically, with no separate change needed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A real, direct check on whether the new Sales Register idea had been logged — it had not, and is now fixed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Checked both sheets directly rather than assume — it was genuinely absent from both</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Feature Tracker and this narrative sheet both searched for 'sales register', 'walk-in', 'point of sale', 'business tools' — no real match in either</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Added as Feature #144, Not started across all three layers, with the full real scope from the conversation captured — not a one-line placeholder</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Walk-in register with shared inventory, credit sales/receivables, categorized expenses, automatic multi-range statements, per-item historical analytics, voice-to-text entry, offline queue with mandatory 24-hour sync, and a simplified Balance Sheet honestly labeled as such</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fixed a real, separate bug found while adding this: the Summary sheet's formulas were hardcoded to row 145 and silently excluded the new row</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COUNTIF ranges extended to 146, recalculated, confirmed the total genuinely reads 144 now, not left at a stale 143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Section-by-section handover-document audit — 2 real findings from the first 4 sections checked</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Real gap #1: credit_requests / restock_requests — a formally specified attendant-to-seller approval workflow, zero matching tables in the live database</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confirmed by direct query, not assumed. The 'attendants never get write access to price/product fields' half of this same spec section IS correctly enforced today via real RLS — only the request/approval workflow itself is missing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Real gap #2 (found and fixed): the P&amp;L Calculator's real original spec was far more detailed than what existed in code</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cost price, selling price, quantity sold, expenses -&gt; real revenue, cost, net profit/loss, profit margin %, and a plain verdict (Healthy profit/Low margin/Break even/Loss). Rebuilt to match exactly, including a genuinely reusable calculation function per the spec's explicit note that it shouldn't be hardcoded to one screen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Both documents updated to match — User Guide Edition 4.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Corrected the P&amp;L description that this session itself had written earlier, since it described the old, simplified version</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 of 18 handover-document sections now checked (0/Brand, 1/Architecture, 2/Seller Dashboard, partial on 6/7/15 from the prior round)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14 sections remain: Product Upload full field set, Brand-Aware Product Database, Pepper/Vegetable pattern, rest of Buyer Marketplace, Repair, Director Dashboard, Kasuwa Price Watch, Used Items, Canteen, Bills &amp; Services, T&amp;C, Fraud &amp; Security Notes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Section 3 (Product Upload Full Field Set) audited — 4 real gaps found, all 4 fixed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gap #1: unit of sale — the column existed but AddListing never set it, confirmed by reading the actual insert() call</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Now a real field on the form, wired into the insert</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gap #2: bulk pricing — no bulk_price/bulk_min_quantity concept existed anywhere (product_variants covers named variants, a different thing)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Real columns added with real server-side constraints: bulk_price genuinely below retail, both fields paired or both null — not just a client-side form check</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gap #3: category_brands — specified as its own lookup table, didn't exist at all</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Created and seeded with the real brand lists explicitly given in the handover document itself — not invented. Phones/Home appliances/Computers categories deliberately left unseeded since the spec only said 'major Nigerian-market brands' with no explicit list for those, matching the established discipline of not inventing data without a real source</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gap #4: fashion/footwear sizing — zero size or colour fields existed anywhere in the schema</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Real size_type, available_sizes, available_colours columns added, real conditional UI on the Add Listing form for fashion/footwear categories, real multi-select colour chips matching the spec's explicit multi-select requirement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stock status (Available/Sold out/Restocked) — checked and found substantively equivalent, not a gap</t>
+  </si>
+  <si>
+    <t xml:space="preserve">products.status (live/sold_out/discontinued) achieves the same real intent — seller-controlled inventory truth — even though exact state names differ from the spec's wording</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Full frontend build verified clean after all four fixes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SellerDashboard chunk grew from 24KB to 29KB to accommodate the real new form fields — still small, still code-split correctly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Section 3 of 18 now fully audited and closed. Sections 4 and 5 (Brand-Aware DB, Pepper/Vegetable pattern) folded into this same round since they were directly tied to Section 3's gaps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15 sections remain: rest of Buyer Marketplace, Repair, Director Dashboard, Kasuwa Price Watch, Used Items, Canteen, Bills &amp; Services, T&amp;C, Fraud &amp; Security Notes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sections 8-11 resolved: two major architecture questions confirmed as deliberate standing decisions, plus a real market-overview gap closed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Multi-seller split settlement vs per-seller checkout — resolved with real evidence, not assumption</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Found checkout_cart()'s own code comment, written the same day the handover doc was uploaded: 'checkout is per-seller by design, matching how orders already work.' This was a conscious, documented engineering decision made after seeing the handover doc's alternative, not an oversight. User confirmed: keep as-is</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Subscription-tier commission vs flat rates — same resolution</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sellers.tier is explicitly commented as a registration category, not a billing tier; no subscription infrastructure was ever built. Flat rates (already implemented this session from the July 17 consulting) match what was actually built structurally. User confirmed: keep as-is</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Instalment/BNPL policy — checked, matches exactly, no gap</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7-day full refund, 20% fee 10/10 split between day 7-90, non-refundable-but-transferable after 90 days</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Real gap found and closed: Kasuwa Price Watch only tracked a buyer's own watched item, never the market-wide commodity comparison the spec envisioned</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Built get_market_price_overview() — real live aggregation (lowest/average/highest price, real seller count, computed best-deal savings) across every open store for a category, not static data. Added as a genuine new 'Market-wide price check' section, distinct from the existing personal watch list</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confirmed still-open gaps from Section 10 (Director Dashboard) carried forward, not re-litigated</t>
+  </si>
+  <si>
+    <t xml:space="preserve">credit_requests/restock_requests (already logged, folds into Feature #144), Supabase Realtime for instant store open/close (zero tables currently enabled), and a persistent cost_price field with real RLS hiding it from attendants (currently only exists as one-time P&amp;L Calculator input, never stored)</t>
   </si>
   <si>
     <t xml:space="preserve">NOT YET STARTED</t>
@@ -4011,7 +4176,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="General"/>
   </numFmts>
-  <fonts count="19">
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4137,6 +4302,14 @@
     </font>
     <font>
       <b val="true"/>
+      <sz val="10"/>
+      <color rgb="FF842029"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
       <sz val="11"/>
       <color rgb="FF8B0000"/>
       <name val="Arial"/>
@@ -4152,7 +4325,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -4180,13 +4353,19 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
-        <bgColor rgb="FFFCE4D6"/>
+        <bgColor rgb="FFF8D7DA"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFCE4D6"/>
-        <bgColor rgb="FFD9E8E3"/>
+        <bgColor rgb="FFF8D7DA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8D7DA"/>
+        <bgColor rgb="FFFCE4D6"/>
       </patternFill>
     </fill>
     <fill>
@@ -4251,7 +4430,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="33">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -4344,19 +4523,31 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="7" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="8" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="18" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -4364,7 +4555,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="18" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="19" fillId="9" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="9" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -4493,13 +4688,13 @@
       <rgbColor rgb="FFCCCCCC"/>
       <rgbColor rgb="FF808080"/>
       <rgbColor rgb="FF9999FF"/>
-      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FF842029"/>
       <rgbColor rgb="FFFCE4D6"/>
       <rgbColor rgb="FFD9E8E3"/>
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
       <rgbColor rgb="FF0066CC"/>
-      <rgbColor rgb="FFCCCCFF"/>
+      <rgbColor rgb="FFF8D7DA"/>
       <rgbColor rgb="FF000080"/>
       <rgbColor rgb="FFFF00FF"/>
       <rgbColor rgb="FFFFFF00"/>
@@ -4926,20 +5121,20 @@
         <v>31</v>
       </c>
       <c r="B5" s="10" t="n">
-        <f aca="false">COUNTIF('Feature Tracker'!F3:F145,"Done")</f>
-        <v>143</v>
+        <f aca="false">COUNTIF('Feature Tracker'!F3:F147,"Done")</f>
+        <v>144</v>
       </c>
       <c r="C5" s="10" t="n">
-        <f aca="false">COUNTIF('Feature Tracker'!F3:F145,"Partial")</f>
+        <f aca="false">COUNTIF('Feature Tracker'!F3:F147,"Partial")</f>
         <v>0</v>
       </c>
       <c r="D5" s="10" t="n">
-        <f aca="false">COUNTIF('Feature Tracker'!F3:F145,"Not started")</f>
-        <v>0</v>
+        <f aca="false">COUNTIF('Feature Tracker'!F3:F147,"Not started")</f>
+        <v>1</v>
       </c>
       <c r="E5" s="10" t="n">
         <f aca="false">SUM(B5:D5)</f>
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4947,20 +5142,20 @@
         <v>32</v>
       </c>
       <c r="B6" s="10" t="n">
-        <f aca="false">COUNTIF('Feature Tracker'!G3:G145,"Done")</f>
+        <f aca="false">COUNTIF('Feature Tracker'!G3:G147,"Done")</f>
         <v>125</v>
       </c>
       <c r="C6" s="10" t="n">
-        <f aca="false">COUNTIF('Feature Tracker'!G3:G145,"Partial")</f>
+        <f aca="false">COUNTIF('Feature Tracker'!G3:G147,"Partial")</f>
         <v>18</v>
       </c>
       <c r="D6" s="10" t="n">
-        <f aca="false">COUNTIF('Feature Tracker'!G3:G145,"Not started")</f>
-        <v>0</v>
+        <f aca="false">COUNTIF('Feature Tracker'!G3:G147,"Not started")</f>
+        <v>2</v>
       </c>
       <c r="E6" s="10" t="n">
         <f aca="false">SUM(B6:D6)</f>
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4968,20 +5163,20 @@
         <v>33</v>
       </c>
       <c r="B7" s="10" t="n">
-        <f aca="false">COUNTIF('Feature Tracker'!H3:H145,"Done")</f>
+        <f aca="false">COUNTIF('Feature Tracker'!H3:H147,"Done")</f>
         <v>135</v>
       </c>
       <c r="C7" s="10" t="n">
-        <f aca="false">COUNTIF('Feature Tracker'!H3:H145,"Partial")</f>
+        <f aca="false">COUNTIF('Feature Tracker'!H3:H147,"Partial")</f>
         <v>1</v>
       </c>
       <c r="D7" s="10" t="n">
-        <f aca="false">COUNTIF('Feature Tracker'!H3:H145,"Not started")</f>
-        <v>7</v>
+        <f aca="false">COUNTIF('Feature Tracker'!H3:H147,"Not started")</f>
+        <v>9</v>
       </c>
       <c r="E7" s="10" t="n">
         <f aca="false">SUM(B7:D7)</f>
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4989,8 +5184,8 @@
         <v>34</v>
       </c>
       <c r="B9" s="11" t="n">
-        <f aca="false">COUNTA('Feature Tracker'!D3:D145)</f>
-        <v>143</v>
+        <f aca="false">COUNTA('Feature Tracker'!D3:D147)</f>
+        <v>145</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5329,7 +5524,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I145"/>
+  <dimension ref="A1:I147"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="5"/>
@@ -9530,6 +9725,64 @@
       </c>
       <c r="I145" s="19" t="s">
         <v>527</v>
+      </c>
+    </row>
+    <row r="146" customFormat="false" ht="270" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A146" s="1" t="n">
+        <v>144</v>
+      </c>
+      <c r="B146" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C146" s="4" t="s">
+        <v>528</v>
+      </c>
+      <c r="D146" s="23" t="s">
+        <v>529</v>
+      </c>
+      <c r="E146" s="4" t="s">
+        <v>530</v>
+      </c>
+      <c r="F146" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="G146" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="H146" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="I146" s="4" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="147" customFormat="false" ht="135.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A147" s="1" t="n">
+        <v>145</v>
+      </c>
+      <c r="B147" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C147" s="4" t="s">
+        <v>532</v>
+      </c>
+      <c r="D147" s="23" t="s">
+        <v>533</v>
+      </c>
+      <c r="E147" s="4" t="s">
+        <v>534</v>
+      </c>
+      <c r="F147" s="25" t="s">
+        <v>27</v>
+      </c>
+      <c r="G147" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="H147" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="I147" s="4" t="s">
+        <v>535</v>
       </c>
     </row>
   </sheetData>
@@ -9559,7 +9812,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C476"/>
+  <dimension ref="A1:C504"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="30"/>
@@ -9569,865 +9822,865 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>528</v>
+        <v>536</v>
       </c>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="7" t="s">
-        <v>529</v>
+        <v>537</v>
       </c>
       <c r="B2" s="7"/>
       <c r="C2" s="7"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="23" t="s">
-        <v>530</v>
-      </c>
-      <c r="B3" s="23" t="s">
-        <v>531</v>
-      </c>
-      <c r="C3" s="23" t="s">
+      <c r="A3" s="26" t="s">
+        <v>538</v>
+      </c>
+      <c r="B3" s="26" t="s">
+        <v>539</v>
+      </c>
+      <c r="C3" s="26" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="24" t="s">
-        <v>532</v>
-      </c>
-      <c r="B4" s="25"/>
-      <c r="C4" s="25"/>
+      <c r="A4" s="27" t="s">
+        <v>540</v>
+      </c>
+      <c r="B4" s="28"/>
+      <c r="C4" s="28"/>
     </row>
     <row r="5" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="17" t="s">
-        <v>533</v>
+        <v>541</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>534</v>
+        <v>542</v>
       </c>
       <c r="C5" s="19" t="s">
-        <v>535</v>
+        <v>543</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="17" t="s">
-        <v>536</v>
+        <v>544</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>537</v>
+        <v>545</v>
       </c>
       <c r="C6" s="19" t="s">
-        <v>538</v>
+        <v>546</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="17" t="s">
-        <v>539</v>
+        <v>547</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>540</v>
+        <v>548</v>
       </c>
       <c r="C7" s="19" t="s">
-        <v>541</v>
+        <v>549</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="17" t="s">
-        <v>542</v>
+        <v>550</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>543</v>
+        <v>551</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>544</v>
+        <v>552</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="24" t="s">
-        <v>545</v>
-      </c>
-      <c r="B9" s="25"/>
-      <c r="C9" s="25"/>
+      <c r="A9" s="27" t="s">
+        <v>553</v>
+      </c>
+      <c r="B9" s="28"/>
+      <c r="C9" s="28"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="17" t="s">
-        <v>546</v>
+        <v>554</v>
       </c>
       <c r="B10" s="16" t="s">
-        <v>547</v>
+        <v>555</v>
       </c>
       <c r="C10" s="19" t="s">
-        <v>548</v>
+        <v>556</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="17" t="s">
-        <v>549</v>
+        <v>557</v>
       </c>
       <c r="B11" s="16" t="s">
-        <v>550</v>
+        <v>558</v>
       </c>
       <c r="C11" s="19" t="s">
-        <v>551</v>
+        <v>559</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="17" t="s">
-        <v>552</v>
+        <v>560</v>
       </c>
       <c r="B12" s="16" t="s">
-        <v>553</v>
+        <v>561</v>
       </c>
       <c r="C12" s="19" t="s">
-        <v>554</v>
+        <v>562</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="17" t="s">
-        <v>555</v>
+        <v>563</v>
       </c>
       <c r="B13" s="16" t="s">
-        <v>556</v>
+        <v>564</v>
       </c>
       <c r="C13" s="19" t="s">
-        <v>557</v>
+        <v>565</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="24" t="s">
-        <v>558</v>
-      </c>
-      <c r="B14" s="25"/>
-      <c r="C14" s="25"/>
+      <c r="A14" s="27" t="s">
+        <v>566</v>
+      </c>
+      <c r="B14" s="28"/>
+      <c r="C14" s="28"/>
     </row>
     <row r="15" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="17" t="s">
-        <v>559</v>
+        <v>567</v>
       </c>
       <c r="B15" s="16" t="s">
-        <v>560</v>
+        <v>568</v>
       </c>
       <c r="C15" s="19" t="s">
-        <v>561</v>
+        <v>569</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="17" t="s">
-        <v>562</v>
+        <v>570</v>
       </c>
       <c r="B16" s="16" t="s">
-        <v>563</v>
+        <v>571</v>
       </c>
       <c r="C16" s="19" t="s">
-        <v>564</v>
+        <v>572</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="17" t="s">
-        <v>565</v>
+        <v>573</v>
       </c>
       <c r="B17" s="16" t="s">
-        <v>566</v>
+        <v>574</v>
       </c>
       <c r="C17" s="19" t="s">
-        <v>567</v>
+        <v>575</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="32.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="17" t="s">
-        <v>568</v>
+        <v>576</v>
       </c>
       <c r="B18" s="16" t="s">
-        <v>569</v>
+        <v>577</v>
       </c>
       <c r="C18" s="19" t="s">
-        <v>570</v>
+        <v>578</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="17" t="s">
-        <v>571</v>
+        <v>579</v>
       </c>
       <c r="B19" s="16" t="s">
-        <v>572</v>
+        <v>580</v>
       </c>
       <c r="C19" s="19" t="s">
-        <v>573</v>
+        <v>581</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="24" t="s">
-        <v>574</v>
-      </c>
-      <c r="B20" s="25"/>
-      <c r="C20" s="25"/>
+      <c r="A20" s="27" t="s">
+        <v>582</v>
+      </c>
+      <c r="B20" s="28"/>
+      <c r="C20" s="28"/>
     </row>
     <row r="21" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="17" t="s">
-        <v>575</v>
+        <v>583</v>
       </c>
       <c r="B21" s="16" t="s">
-        <v>576</v>
+        <v>584</v>
       </c>
       <c r="C21" s="19" t="s">
-        <v>577</v>
+        <v>585</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="17" t="s">
-        <v>578</v>
+        <v>586</v>
       </c>
       <c r="B22" s="16" t="s">
-        <v>579</v>
+        <v>587</v>
       </c>
       <c r="C22" s="19" t="s">
-        <v>580</v>
+        <v>588</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="17" t="s">
-        <v>581</v>
+        <v>589</v>
       </c>
       <c r="B23" s="16" t="s">
-        <v>582</v>
+        <v>590</v>
       </c>
       <c r="C23" s="19" t="s">
-        <v>583</v>
+        <v>591</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="17" t="s">
-        <v>584</v>
+        <v>592</v>
       </c>
       <c r="B24" s="16" t="s">
-        <v>585</v>
+        <v>593</v>
       </c>
       <c r="C24" s="19" t="s">
-        <v>586</v>
+        <v>594</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="17" t="s">
-        <v>587</v>
+        <v>595</v>
       </c>
       <c r="B25" s="16" t="s">
-        <v>588</v>
+        <v>596</v>
       </c>
       <c r="C25" s="19" t="s">
-        <v>589</v>
+        <v>597</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="17" t="s">
-        <v>590</v>
+        <v>598</v>
       </c>
       <c r="B26" s="16" t="s">
-        <v>591</v>
+        <v>599</v>
       </c>
       <c r="C26" s="19" t="s">
-        <v>592</v>
+        <v>600</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="17" t="s">
-        <v>593</v>
+        <v>601</v>
       </c>
       <c r="B27" s="16" t="s">
-        <v>594</v>
+        <v>602</v>
       </c>
       <c r="C27" s="19" t="s">
-        <v>595</v>
+        <v>603</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="17" t="s">
-        <v>596</v>
+        <v>604</v>
       </c>
       <c r="B28" s="16" t="s">
-        <v>597</v>
+        <v>605</v>
       </c>
       <c r="C28" s="19" t="s">
-        <v>598</v>
+        <v>606</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="17" t="s">
-        <v>599</v>
+        <v>607</v>
       </c>
       <c r="B29" s="16" t="s">
-        <v>600</v>
+        <v>608</v>
       </c>
       <c r="C29" s="19" t="s">
-        <v>601</v>
+        <v>609</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="24" t="s">
-        <v>602</v>
-      </c>
-      <c r="B30" s="25"/>
-      <c r="C30" s="25"/>
+      <c r="A30" s="27" t="s">
+        <v>610</v>
+      </c>
+      <c r="B30" s="28"/>
+      <c r="C30" s="28"/>
     </row>
     <row r="31" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="17" t="s">
-        <v>603</v>
+        <v>611</v>
       </c>
       <c r="B31" s="16" t="s">
-        <v>604</v>
+        <v>612</v>
       </c>
       <c r="C31" s="19" t="s">
-        <v>605</v>
+        <v>613</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="17" t="s">
-        <v>606</v>
+        <v>614</v>
       </c>
       <c r="B32" s="16" t="s">
-        <v>607</v>
+        <v>615</v>
       </c>
       <c r="C32" s="19" t="s">
-        <v>608</v>
+        <v>616</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="17" t="s">
-        <v>609</v>
+        <v>617</v>
       </c>
       <c r="B33" s="16" t="s">
-        <v>610</v>
+        <v>618</v>
       </c>
       <c r="C33" s="19" t="s">
-        <v>611</v>
+        <v>619</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="17" t="s">
-        <v>612</v>
+        <v>620</v>
       </c>
       <c r="B34" s="16" t="s">
-        <v>613</v>
+        <v>621</v>
       </c>
       <c r="C34" s="19" t="s">
-        <v>614</v>
+        <v>622</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="17" t="s">
-        <v>615</v>
+        <v>623</v>
       </c>
       <c r="B35" s="16" t="s">
-        <v>616</v>
+        <v>624</v>
       </c>
       <c r="C35" s="19"/>
     </row>
     <row r="36" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="17" t="s">
-        <v>617</v>
+        <v>625</v>
       </c>
       <c r="B36" s="16" t="s">
-        <v>618</v>
+        <v>626</v>
       </c>
       <c r="C36" s="19" t="s">
-        <v>619</v>
+        <v>627</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="24" t="s">
-        <v>620</v>
-      </c>
-      <c r="B39" s="25"/>
-      <c r="C39" s="25"/>
+      <c r="A39" s="27" t="s">
+        <v>628</v>
+      </c>
+      <c r="B39" s="28"/>
+      <c r="C39" s="28"/>
     </row>
     <row r="40" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="17" t="s">
-        <v>621</v>
+        <v>629</v>
       </c>
       <c r="B40" s="16" t="s">
-        <v>622</v>
+        <v>630</v>
       </c>
       <c r="C40" s="19" t="s">
-        <v>623</v>
+        <v>631</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="17" t="s">
-        <v>624</v>
+        <v>632</v>
       </c>
       <c r="B41" s="16" t="s">
-        <v>625</v>
+        <v>633</v>
       </c>
       <c r="C41" s="19" t="s">
-        <v>626</v>
+        <v>634</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="17" t="s">
-        <v>627</v>
+        <v>635</v>
       </c>
       <c r="B42" s="16" t="s">
-        <v>628</v>
+        <v>636</v>
       </c>
       <c r="C42" s="19" t="s">
-        <v>629</v>
+        <v>637</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="17" t="s">
-        <v>630</v>
+        <v>638</v>
       </c>
       <c r="B43" s="16" t="s">
-        <v>631</v>
+        <v>639</v>
       </c>
       <c r="C43" s="19" t="s">
-        <v>632</v>
+        <v>640</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="17" t="s">
-        <v>633</v>
+        <v>641</v>
       </c>
       <c r="B44" s="16" t="s">
-        <v>634</v>
+        <v>642</v>
       </c>
       <c r="C44" s="19" t="s">
-        <v>635</v>
+        <v>643</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A47" s="24" t="s">
-        <v>636</v>
-      </c>
-      <c r="B47" s="25"/>
-      <c r="C47" s="25"/>
+      <c r="A47" s="27" t="s">
+        <v>644</v>
+      </c>
+      <c r="B47" s="28"/>
+      <c r="C47" s="28"/>
     </row>
     <row r="48" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="17" t="s">
-        <v>637</v>
+        <v>645</v>
       </c>
       <c r="B48" s="16" t="s">
-        <v>638</v>
+        <v>646</v>
       </c>
       <c r="C48" s="19" t="s">
-        <v>639</v>
+        <v>647</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="17" t="s">
-        <v>640</v>
+        <v>648</v>
       </c>
       <c r="B49" s="16" t="s">
-        <v>641</v>
+        <v>649</v>
       </c>
       <c r="C49" s="19" t="s">
-        <v>642</v>
+        <v>650</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="51" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="52" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A52" s="24" t="s">
-        <v>643</v>
-      </c>
-      <c r="B52" s="25"/>
-      <c r="C52" s="25"/>
+      <c r="A52" s="27" t="s">
+        <v>651</v>
+      </c>
+      <c r="B52" s="28"/>
+      <c r="C52" s="28"/>
     </row>
     <row r="53" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="17" t="s">
-        <v>644</v>
+        <v>652</v>
       </c>
       <c r="B53" s="16" t="s">
-        <v>645</v>
+        <v>653</v>
       </c>
       <c r="C53" s="19" t="s">
-        <v>646</v>
+        <v>654</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="17" t="s">
-        <v>647</v>
+        <v>655</v>
       </c>
       <c r="B54" s="16" t="s">
-        <v>648</v>
+        <v>656</v>
       </c>
       <c r="C54" s="19"/>
     </row>
     <row r="55" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="17" t="s">
-        <v>649</v>
+        <v>657</v>
       </c>
       <c r="B55" s="16" t="s">
-        <v>650</v>
+        <v>658</v>
       </c>
       <c r="C55" s="19" t="s">
-        <v>651</v>
+        <v>659</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="17" t="s">
-        <v>652</v>
+        <v>660</v>
       </c>
       <c r="B56" s="16" t="s">
-        <v>653</v>
+        <v>661</v>
       </c>
       <c r="C56" s="19" t="s">
-        <v>654</v>
+        <v>662</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="17" t="s">
-        <v>655</v>
+        <v>663</v>
       </c>
       <c r="B57" s="16" t="s">
-        <v>656</v>
+        <v>664</v>
       </c>
       <c r="C57" s="19" t="s">
-        <v>657</v>
+        <v>665</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="17" t="s">
-        <v>658</v>
+        <v>666</v>
       </c>
       <c r="B58" s="16" t="s">
-        <v>659</v>
+        <v>667</v>
       </c>
       <c r="C58" s="19" t="s">
-        <v>660</v>
+        <v>668</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A60" s="24" t="s">
-        <v>661</v>
-      </c>
-      <c r="B60" s="25"/>
-      <c r="C60" s="25"/>
+      <c r="A60" s="27" t="s">
+        <v>669</v>
+      </c>
+      <c r="B60" s="28"/>
+      <c r="C60" s="28"/>
     </row>
     <row r="61" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="17" t="s">
-        <v>662</v>
+        <v>670</v>
       </c>
       <c r="B61" s="16" t="s">
-        <v>663</v>
+        <v>671</v>
       </c>
       <c r="C61" s="19" t="s">
-        <v>664</v>
+        <v>672</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="17" t="s">
-        <v>665</v>
+        <v>673</v>
       </c>
       <c r="B62" s="16" t="s">
-        <v>666</v>
+        <v>674</v>
       </c>
       <c r="C62" s="19"/>
     </row>
     <row r="63" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="17" t="s">
-        <v>667</v>
+        <v>675</v>
       </c>
       <c r="B63" s="16" t="s">
-        <v>668</v>
+        <v>676</v>
       </c>
       <c r="C63" s="19"/>
     </row>
     <row r="64" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="17" t="s">
-        <v>669</v>
+        <v>677</v>
       </c>
       <c r="B64" s="16" t="s">
-        <v>670</v>
+        <v>678</v>
       </c>
       <c r="C64" s="19" t="s">
-        <v>671</v>
+        <v>679</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="17" t="s">
-        <v>672</v>
+        <v>680</v>
       </c>
       <c r="B65" s="16" t="s">
-        <v>673</v>
+        <v>681</v>
       </c>
       <c r="C65" s="19" t="s">
-        <v>674</v>
+        <v>682</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A68" s="24" t="s">
-        <v>675</v>
-      </c>
-      <c r="B68" s="25"/>
-      <c r="C68" s="25"/>
+      <c r="A68" s="27" t="s">
+        <v>683</v>
+      </c>
+      <c r="B68" s="28"/>
+      <c r="C68" s="28"/>
     </row>
     <row r="69" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="17" t="s">
-        <v>676</v>
+        <v>684</v>
       </c>
       <c r="B69" s="16" t="s">
-        <v>677</v>
+        <v>685</v>
       </c>
       <c r="C69" s="19" t="s">
-        <v>678</v>
+        <v>686</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="17" t="s">
-        <v>679</v>
+        <v>687</v>
       </c>
       <c r="B70" s="16" t="s">
-        <v>680</v>
+        <v>688</v>
       </c>
       <c r="C70" s="19" t="s">
-        <v>681</v>
+        <v>689</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A71" s="24" t="s">
-        <v>682</v>
-      </c>
-      <c r="B71" s="25"/>
-      <c r="C71" s="25"/>
+      <c r="A71" s="27" t="s">
+        <v>690</v>
+      </c>
+      <c r="B71" s="28"/>
+      <c r="C71" s="28"/>
     </row>
     <row r="72" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="17" t="s">
-        <v>683</v>
+        <v>691</v>
       </c>
       <c r="B72" s="16" t="s">
-        <v>684</v>
+        <v>692</v>
       </c>
       <c r="C72" s="19" t="s">
-        <v>685</v>
+        <v>693</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="17" t="s">
-        <v>686</v>
+        <v>694</v>
       </c>
       <c r="B73" s="16" t="s">
-        <v>687</v>
+        <v>695</v>
       </c>
       <c r="C73" s="19" t="s">
-        <v>688</v>
+        <v>696</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A74" s="24" t="s">
-        <v>689</v>
-      </c>
-      <c r="B74" s="25"/>
-      <c r="C74" s="25"/>
+      <c r="A74" s="27" t="s">
+        <v>697</v>
+      </c>
+      <c r="B74" s="28"/>
+      <c r="C74" s="28"/>
     </row>
     <row r="75" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="17" t="s">
-        <v>690</v>
+        <v>698</v>
       </c>
       <c r="B75" s="16" t="s">
-        <v>691</v>
+        <v>699</v>
       </c>
       <c r="C75" s="19"/>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="17" t="s">
-        <v>692</v>
+        <v>700</v>
       </c>
       <c r="B76" s="16" t="s">
-        <v>693</v>
+        <v>701</v>
       </c>
       <c r="C76" s="19"/>
     </row>
     <row r="77" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="17" t="s">
-        <v>694</v>
+        <v>702</v>
       </c>
       <c r="B77" s="16" t="s">
-        <v>695</v>
+        <v>703</v>
       </c>
       <c r="C77" s="19"/>
     </row>
     <row r="78" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A78" s="17" t="s">
-        <v>696</v>
+        <v>704</v>
       </c>
       <c r="B78" s="16" t="s">
-        <v>697</v>
+        <v>705</v>
       </c>
       <c r="C78" s="19"/>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A79" s="24" t="s">
-        <v>698</v>
-      </c>
-      <c r="B79" s="25"/>
-      <c r="C79" s="25"/>
+      <c r="A79" s="27" t="s">
+        <v>706</v>
+      </c>
+      <c r="B79" s="28"/>
+      <c r="C79" s="28"/>
     </row>
     <row r="80" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A80" s="17" t="s">
-        <v>699</v>
+        <v>707</v>
       </c>
       <c r="B80" s="16" t="s">
-        <v>700</v>
+        <v>708</v>
       </c>
       <c r="C80" s="19" t="s">
-        <v>701</v>
+        <v>709</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A81" s="17" t="s">
-        <v>683</v>
+        <v>691</v>
       </c>
       <c r="B81" s="16" t="s">
-        <v>702</v>
+        <v>710</v>
       </c>
       <c r="C81" s="19"/>
     </row>
     <row r="82" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A82" s="17" t="s">
-        <v>686</v>
+        <v>694</v>
       </c>
       <c r="B82" s="16" t="s">
-        <v>703</v>
+        <v>711</v>
       </c>
       <c r="C82" s="19" t="s">
-        <v>704</v>
+        <v>712</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A83" s="17" t="s">
-        <v>690</v>
+        <v>698</v>
       </c>
       <c r="B83" s="16" t="s">
-        <v>705</v>
+        <v>713</v>
       </c>
       <c r="C83" s="19"/>
     </row>
     <row r="84" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A84" s="17" t="s">
-        <v>692</v>
+        <v>700</v>
       </c>
       <c r="B84" s="16" t="s">
-        <v>706</v>
+        <v>714</v>
       </c>
       <c r="C84" s="19"/>
     </row>
     <row r="85" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A85" s="17" t="s">
-        <v>696</v>
+        <v>704</v>
       </c>
       <c r="B85" s="16" t="s">
-        <v>707</v>
+        <v>715</v>
       </c>
       <c r="C85" s="19"/>
     </row>
     <row r="86" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A86" s="17" t="s">
-        <v>708</v>
+        <v>716</v>
       </c>
       <c r="B86" s="16" t="s">
-        <v>709</v>
+        <v>717</v>
       </c>
       <c r="C86" s="19" t="s">
-        <v>710</v>
+        <v>718</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A88" s="24" t="s">
-        <v>711</v>
-      </c>
-      <c r="B88" s="25"/>
-      <c r="C88" s="25"/>
+      <c r="A88" s="27" t="s">
+        <v>719</v>
+      </c>
+      <c r="B88" s="28"/>
+      <c r="C88" s="28"/>
     </row>
     <row r="89" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A89" s="17" t="s">
-        <v>712</v>
+        <v>720</v>
       </c>
       <c r="B89" s="16" t="s">
-        <v>713</v>
+        <v>721</v>
       </c>
       <c r="C89" s="19"/>
     </row>
     <row r="90" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A90" s="17" t="s">
-        <v>714</v>
+        <v>722</v>
       </c>
       <c r="B90" s="16" t="s">
-        <v>715</v>
+        <v>723</v>
       </c>
       <c r="C90" s="19"/>
     </row>
     <row r="91" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A91" s="17" t="s">
-        <v>716</v>
+        <v>724</v>
       </c>
       <c r="B91" s="16" t="s">
-        <v>717</v>
+        <v>725</v>
       </c>
       <c r="C91" s="19"/>
     </row>
     <row r="92" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A92" s="17" t="s">
-        <v>718</v>
+        <v>726</v>
       </c>
       <c r="B92" s="16" t="s">
-        <v>719</v>
+        <v>727</v>
       </c>
       <c r="C92" s="19"/>
     </row>
     <row r="93" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A93" s="17" t="s">
-        <v>720</v>
+        <v>728</v>
       </c>
       <c r="B93" s="16" t="s">
-        <v>721</v>
+        <v>729</v>
       </c>
       <c r="C93" s="19"/>
     </row>
     <row r="94" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A94" s="17" t="s">
-        <v>722</v>
+        <v>730</v>
       </c>
       <c r="B94" s="16" t="s">
-        <v>723</v>
+        <v>731</v>
       </c>
       <c r="C94" s="19"/>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A97" s="24" t="s">
-        <v>724</v>
-      </c>
-      <c r="B97" s="25"/>
-      <c r="C97" s="25"/>
+      <c r="A97" s="27" t="s">
+        <v>732</v>
+      </c>
+      <c r="B97" s="28"/>
+      <c r="C97" s="28"/>
     </row>
     <row r="98" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A98" s="17" t="s">
-        <v>725</v>
+        <v>733</v>
       </c>
       <c r="B98" s="16" t="s">
-        <v>726</v>
+        <v>734</v>
       </c>
       <c r="C98" s="19" t="s">
-        <v>727</v>
+        <v>735</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A99" s="17" t="s">
-        <v>728</v>
+        <v>736</v>
       </c>
       <c r="B99" s="16" t="s">
-        <v>729</v>
+        <v>737</v>
       </c>
       <c r="C99" s="19"/>
     </row>
     <row r="100" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A100" s="17" t="s">
-        <v>730</v>
+        <v>738</v>
       </c>
       <c r="B100" s="16" t="s">
-        <v>731</v>
+        <v>739</v>
       </c>
       <c r="C100" s="19"/>
     </row>
@@ -10435,214 +10688,214 @@
     <row r="102" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="103" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A104" s="24" t="s">
-        <v>732</v>
-      </c>
-      <c r="B104" s="25"/>
-      <c r="C104" s="25"/>
+      <c r="A104" s="27" t="s">
+        <v>740</v>
+      </c>
+      <c r="B104" s="28"/>
+      <c r="C104" s="28"/>
     </row>
     <row r="105" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A105" s="17" t="s">
-        <v>733</v>
+        <v>741</v>
       </c>
       <c r="B105" s="16" t="s">
-        <v>734</v>
+        <v>742</v>
       </c>
       <c r="C105" s="19" t="s">
-        <v>735</v>
+        <v>743</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A106" s="17" t="s">
-        <v>736</v>
+        <v>744</v>
       </c>
       <c r="B106" s="16" t="s">
-        <v>737</v>
+        <v>745</v>
       </c>
       <c r="C106" s="19"/>
     </row>
     <row r="107" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A107" s="17" t="s">
-        <v>738</v>
+        <v>746</v>
       </c>
       <c r="B107" s="16" t="s">
-        <v>739</v>
+        <v>747</v>
       </c>
       <c r="C107" s="19"/>
     </row>
     <row r="108" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A108" s="17" t="s">
-        <v>740</v>
+        <v>748</v>
       </c>
       <c r="B108" s="16" t="s">
-        <v>741</v>
+        <v>749</v>
       </c>
       <c r="C108" s="19"/>
     </row>
     <row r="109" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="110" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A111" s="24" t="s">
-        <v>742</v>
-      </c>
-      <c r="B111" s="25"/>
-      <c r="C111" s="25"/>
+      <c r="A111" s="27" t="s">
+        <v>750</v>
+      </c>
+      <c r="B111" s="28"/>
+      <c r="C111" s="28"/>
     </row>
     <row r="112" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A112" s="17" t="s">
-        <v>743</v>
+        <v>751</v>
       </c>
       <c r="B112" s="16" t="s">
-        <v>744</v>
+        <v>752</v>
       </c>
       <c r="C112" s="19"/>
     </row>
     <row r="113" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A113" s="17" t="s">
-        <v>745</v>
+        <v>753</v>
       </c>
       <c r="B113" s="16" t="s">
-        <v>746</v>
+        <v>754</v>
       </c>
       <c r="C113" s="19"/>
     </row>
     <row r="114" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A114" s="17" t="s">
-        <v>747</v>
+        <v>755</v>
       </c>
       <c r="B114" s="16" t="s">
-        <v>748</v>
+        <v>756</v>
       </c>
       <c r="C114" s="19"/>
     </row>
     <row r="115" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A115" s="17" t="s">
-        <v>749</v>
+        <v>757</v>
       </c>
       <c r="B115" s="16" t="s">
-        <v>750</v>
+        <v>758</v>
       </c>
       <c r="C115" s="19"/>
     </row>
     <row r="116" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A116" s="17" t="s">
-        <v>751</v>
+        <v>759</v>
       </c>
       <c r="B116" s="16" t="s">
-        <v>752</v>
+        <v>760</v>
       </c>
       <c r="C116" s="19"/>
     </row>
     <row r="117" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A117" s="17" t="s">
-        <v>753</v>
+        <v>761</v>
       </c>
       <c r="B117" s="16" t="s">
-        <v>754</v>
+        <v>762</v>
       </c>
       <c r="C117" s="19"/>
     </row>
     <row r="118" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A118" s="17" t="s">
-        <v>755</v>
+        <v>763</v>
       </c>
       <c r="B118" s="16" t="s">
-        <v>756</v>
+        <v>764</v>
       </c>
       <c r="C118" s="19"/>
     </row>
     <row r="122" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A122" s="24" t="s">
-        <v>757</v>
-      </c>
-      <c r="B122" s="25"/>
-      <c r="C122" s="25"/>
+      <c r="A122" s="27" t="s">
+        <v>765</v>
+      </c>
+      <c r="B122" s="28"/>
+      <c r="C122" s="28"/>
     </row>
     <row r="123" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A123" s="17" t="s">
-        <v>758</v>
+        <v>766</v>
       </c>
       <c r="B123" s="16" t="s">
-        <v>759</v>
+        <v>767</v>
       </c>
       <c r="C123" s="19"/>
     </row>
     <row r="124" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A124" s="17" t="s">
-        <v>760</v>
+        <v>768</v>
       </c>
       <c r="B124" s="16" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="C124" s="19"/>
     </row>
     <row r="125" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A125" s="17" t="s">
-        <v>762</v>
+        <v>770</v>
       </c>
       <c r="B125" s="16" t="s">
-        <v>763</v>
+        <v>771</v>
       </c>
       <c r="C125" s="19"/>
     </row>
     <row r="126" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A126" s="17" t="s">
-        <v>764</v>
+        <v>772</v>
       </c>
       <c r="B126" s="16" t="s">
-        <v>765</v>
+        <v>773</v>
       </c>
       <c r="C126" s="19"/>
     </row>
     <row r="127" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A127" s="17" t="s">
-        <v>766</v>
+        <v>774</v>
       </c>
       <c r="B127" s="16" t="s">
-        <v>767</v>
+        <v>775</v>
       </c>
       <c r="C127" s="19"/>
     </row>
     <row r="128" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A128" s="17" t="s">
-        <v>768</v>
+        <v>776</v>
       </c>
       <c r="B128" s="16" t="s">
-        <v>769</v>
+        <v>777</v>
       </c>
       <c r="C128" s="19"/>
     </row>
     <row r="130" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A130" s="24" t="s">
-        <v>770</v>
-      </c>
-      <c r="B130" s="25"/>
-      <c r="C130" s="25"/>
+      <c r="A130" s="27" t="s">
+        <v>778</v>
+      </c>
+      <c r="B130" s="28"/>
+      <c r="C130" s="28"/>
     </row>
     <row r="131" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A131" s="17" t="s">
-        <v>771</v>
+        <v>779</v>
       </c>
       <c r="B131" s="16" t="s">
-        <v>772</v>
+        <v>780</v>
       </c>
       <c r="C131" s="19"/>
     </row>
     <row r="132" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A132" s="17" t="s">
-        <v>773</v>
+        <v>781</v>
       </c>
       <c r="B132" s="16" t="s">
-        <v>774</v>
+        <v>782</v>
       </c>
       <c r="C132" s="19"/>
     </row>
     <row r="133" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A133" s="17" t="s">
-        <v>775</v>
+        <v>783</v>
       </c>
       <c r="B133" s="16" t="s">
-        <v>776</v>
+        <v>784</v>
       </c>
       <c r="C133" s="19"/>
     </row>
@@ -10650,2641 +10903,2866 @@
     <row r="135" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="136" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="137" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A137" s="24" t="s">
-        <v>777</v>
-      </c>
-      <c r="B137" s="25"/>
-      <c r="C137" s="25"/>
+      <c r="A137" s="27" t="s">
+        <v>785</v>
+      </c>
+      <c r="B137" s="28"/>
+      <c r="C137" s="28"/>
     </row>
     <row r="138" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A138" s="17" t="s">
-        <v>778</v>
+        <v>786</v>
       </c>
       <c r="B138" s="16" t="s">
-        <v>779</v>
+        <v>787</v>
       </c>
       <c r="C138" s="19"/>
     </row>
     <row r="139" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A139" s="17" t="s">
-        <v>780</v>
+        <v>788</v>
       </c>
       <c r="B139" s="16" t="s">
-        <v>781</v>
+        <v>789</v>
       </c>
       <c r="C139" s="19"/>
     </row>
     <row r="140" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A140" s="17" t="s">
-        <v>782</v>
+        <v>790</v>
       </c>
       <c r="B140" s="16" t="s">
-        <v>783</v>
+        <v>791</v>
       </c>
       <c r="C140" s="19"/>
     </row>
     <row r="141" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A141" s="17" t="s">
-        <v>784</v>
+        <v>792</v>
       </c>
       <c r="B141" s="16" t="s">
-        <v>785</v>
+        <v>793</v>
       </c>
       <c r="C141" s="19"/>
     </row>
     <row r="142" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="143" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="144" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A144" s="24" t="s">
-        <v>786</v>
-      </c>
-      <c r="B144" s="25"/>
-      <c r="C144" s="25"/>
+      <c r="A144" s="27" t="s">
+        <v>794</v>
+      </c>
+      <c r="B144" s="28"/>
+      <c r="C144" s="28"/>
     </row>
     <row r="145" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A145" s="17" t="s">
-        <v>787</v>
+        <v>795</v>
       </c>
       <c r="B145" s="16" t="s">
-        <v>788</v>
+        <v>796</v>
       </c>
       <c r="C145" s="19"/>
     </row>
     <row r="146" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A146" s="17" t="s">
-        <v>789</v>
+        <v>797</v>
       </c>
       <c r="B146" s="16" t="s">
-        <v>790</v>
+        <v>798</v>
       </c>
       <c r="C146" s="19"/>
     </row>
     <row r="147" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A147" s="17" t="s">
-        <v>791</v>
+        <v>799</v>
       </c>
       <c r="B147" s="16" t="s">
-        <v>792</v>
+        <v>800</v>
       </c>
       <c r="C147" s="19"/>
     </row>
     <row r="148" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A148" s="17" t="s">
-        <v>793</v>
+        <v>801</v>
       </c>
       <c r="B148" s="16" t="s">
-        <v>794</v>
+        <v>802</v>
       </c>
       <c r="C148" s="19"/>
     </row>
     <row r="149" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A149" s="17" t="s">
-        <v>795</v>
+        <v>803</v>
       </c>
       <c r="B149" s="16" t="s">
-        <v>796</v>
+        <v>804</v>
       </c>
       <c r="C149" s="19"/>
     </row>
     <row r="150" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A150" s="17" t="s">
-        <v>797</v>
+        <v>805</v>
       </c>
       <c r="B150" s="16" t="s">
-        <v>798</v>
+        <v>806</v>
       </c>
       <c r="C150" s="19"/>
     </row>
     <row r="153" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A153" s="24" t="s">
-        <v>799</v>
-      </c>
-      <c r="B153" s="25"/>
-      <c r="C153" s="25"/>
+      <c r="A153" s="27" t="s">
+        <v>807</v>
+      </c>
+      <c r="B153" s="28"/>
+      <c r="C153" s="28"/>
     </row>
     <row r="154" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A154" s="17" t="s">
-        <v>800</v>
+        <v>808</v>
       </c>
       <c r="B154" s="16" t="s">
-        <v>801</v>
+        <v>809</v>
       </c>
       <c r="C154" s="19"/>
     </row>
     <row r="155" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A155" s="17" t="s">
-        <v>802</v>
+        <v>810</v>
       </c>
       <c r="B155" s="16" t="s">
-        <v>803</v>
+        <v>811</v>
       </c>
       <c r="C155" s="19"/>
     </row>
     <row r="156" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A156" s="17" t="s">
-        <v>804</v>
+        <v>812</v>
       </c>
       <c r="B156" s="16" t="s">
-        <v>805</v>
+        <v>813</v>
       </c>
       <c r="C156" s="19"/>
     </row>
     <row r="157" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A157" s="17" t="s">
-        <v>806</v>
+        <v>814</v>
       </c>
       <c r="B157" s="16" t="s">
-        <v>807</v>
+        <v>815</v>
       </c>
       <c r="C157" s="19"/>
     </row>
     <row r="158" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A158" s="17" t="s">
-        <v>808</v>
+        <v>816</v>
       </c>
       <c r="B158" s="16" t="s">
-        <v>809</v>
+        <v>817</v>
       </c>
       <c r="C158" s="19"/>
     </row>
     <row r="159" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A159" s="24" t="s">
-        <v>810</v>
-      </c>
-      <c r="B159" s="25"/>
-      <c r="C159" s="25"/>
+      <c r="A159" s="27" t="s">
+        <v>818</v>
+      </c>
+      <c r="B159" s="28"/>
+      <c r="C159" s="28"/>
     </row>
     <row r="160" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A160" s="17" t="s">
-        <v>811</v>
+        <v>819</v>
       </c>
       <c r="B160" s="16" t="s">
-        <v>812</v>
+        <v>820</v>
       </c>
       <c r="C160" s="19"/>
     </row>
     <row r="161" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A161" s="17" t="s">
-        <v>813</v>
+        <v>821</v>
       </c>
       <c r="B161" s="16" t="s">
-        <v>814</v>
+        <v>822</v>
       </c>
       <c r="C161" s="19"/>
     </row>
     <row r="162" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A162" s="17" t="s">
-        <v>815</v>
+        <v>823</v>
       </c>
       <c r="B162" s="16" t="s">
-        <v>816</v>
+        <v>824</v>
       </c>
       <c r="C162" s="19"/>
     </row>
     <row r="163" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A163" s="17" t="s">
-        <v>817</v>
+        <v>825</v>
       </c>
       <c r="B163" s="16" t="s">
-        <v>818</v>
+        <v>826</v>
       </c>
       <c r="C163" s="19"/>
     </row>
     <row r="164" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A164" s="17" t="s">
-        <v>819</v>
+        <v>827</v>
       </c>
       <c r="B164" s="16" t="s">
-        <v>820</v>
+        <v>828</v>
       </c>
       <c r="C164" s="19"/>
     </row>
     <row r="165" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A165" s="17" t="s">
-        <v>821</v>
+        <v>829</v>
       </c>
       <c r="B165" s="16" t="s">
-        <v>822</v>
+        <v>830</v>
       </c>
       <c r="C165" s="19"/>
     </row>
     <row r="166" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A166" s="24" t="s">
-        <v>823</v>
-      </c>
-      <c r="B166" s="25"/>
-      <c r="C166" s="25"/>
+      <c r="A166" s="27" t="s">
+        <v>831</v>
+      </c>
+      <c r="B166" s="28"/>
+      <c r="C166" s="28"/>
     </row>
     <row r="167" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A167" s="17" t="s">
-        <v>824</v>
+        <v>832</v>
       </c>
       <c r="B167" s="16" t="s">
-        <v>825</v>
+        <v>833</v>
       </c>
       <c r="C167" s="19"/>
     </row>
     <row r="168" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A168" s="17" t="s">
-        <v>826</v>
+        <v>834</v>
       </c>
       <c r="B168" s="16" t="s">
-        <v>827</v>
+        <v>835</v>
       </c>
       <c r="C168" s="19"/>
     </row>
     <row r="169" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A169" s="17" t="s">
-        <v>828</v>
+        <v>836</v>
       </c>
       <c r="B169" s="16" t="s">
-        <v>829</v>
+        <v>837</v>
       </c>
       <c r="C169" s="19"/>
     </row>
     <row r="170" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A170" s="17" t="s">
-        <v>830</v>
+        <v>838</v>
       </c>
       <c r="B170" s="16" t="s">
-        <v>831</v>
+        <v>839</v>
       </c>
       <c r="C170" s="19"/>
     </row>
     <row r="171" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="172" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A172" s="24" t="s">
-        <v>832</v>
-      </c>
-      <c r="B172" s="25"/>
-      <c r="C172" s="25"/>
+      <c r="A172" s="27" t="s">
+        <v>840</v>
+      </c>
+      <c r="B172" s="28"/>
+      <c r="C172" s="28"/>
     </row>
     <row r="173" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A173" s="17" t="s">
-        <v>833</v>
+        <v>841</v>
       </c>
       <c r="B173" s="16" t="s">
-        <v>834</v>
+        <v>842</v>
       </c>
       <c r="C173" s="19"/>
     </row>
     <row r="174" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A174" s="17" t="s">
-        <v>835</v>
+        <v>843</v>
       </c>
       <c r="B174" s="16" t="s">
-        <v>836</v>
+        <v>844</v>
       </c>
       <c r="C174" s="19"/>
     </row>
     <row r="175" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A175" s="17" t="s">
-        <v>837</v>
+        <v>845</v>
       </c>
       <c r="B175" s="16" t="s">
-        <v>838</v>
+        <v>846</v>
       </c>
       <c r="C175" s="19"/>
     </row>
     <row r="176" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A176" s="17" t="s">
-        <v>839</v>
+        <v>847</v>
       </c>
       <c r="B176" s="16" t="s">
-        <v>840</v>
+        <v>848</v>
       </c>
       <c r="C176" s="19"/>
     </row>
     <row r="177" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A177" s="17" t="s">
-        <v>841</v>
+        <v>849</v>
       </c>
       <c r="B177" s="16" t="s">
-        <v>842</v>
+        <v>850</v>
       </c>
       <c r="C177" s="19"/>
     </row>
     <row r="178" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A178" s="17" t="s">
-        <v>843</v>
+        <v>851</v>
       </c>
       <c r="B178" s="16" t="s">
-        <v>844</v>
+        <v>852</v>
       </c>
       <c r="C178" s="19"/>
     </row>
     <row r="180" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A180" s="24" t="s">
-        <v>845</v>
-      </c>
-      <c r="B180" s="25"/>
-      <c r="C180" s="25"/>
+      <c r="A180" s="27" t="s">
+        <v>853</v>
+      </c>
+      <c r="B180" s="28"/>
+      <c r="C180" s="28"/>
     </row>
     <row r="181" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A181" s="17" t="s">
-        <v>846</v>
+        <v>854</v>
       </c>
       <c r="B181" s="16" t="s">
-        <v>847</v>
+        <v>855</v>
       </c>
       <c r="C181" s="19"/>
     </row>
     <row r="182" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A182" s="17" t="s">
-        <v>848</v>
+        <v>856</v>
       </c>
       <c r="B182" s="16" t="s">
-        <v>849</v>
+        <v>857</v>
       </c>
       <c r="C182" s="19"/>
     </row>
     <row r="183" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A183" s="17" t="s">
-        <v>850</v>
+        <v>858</v>
       </c>
       <c r="B183" s="16" t="s">
-        <v>851</v>
+        <v>859</v>
       </c>
       <c r="C183" s="19"/>
     </row>
     <row r="184" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A184" s="17" t="s">
-        <v>852</v>
+        <v>860</v>
       </c>
       <c r="B184" s="16" t="s">
-        <v>853</v>
+        <v>861</v>
       </c>
       <c r="C184" s="19"/>
     </row>
     <row r="185" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A185" s="17" t="s">
-        <v>854</v>
+        <v>862</v>
       </c>
       <c r="B185" s="16" t="s">
-        <v>855</v>
+        <v>863</v>
       </c>
       <c r="C185" s="19"/>
     </row>
     <row r="186" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A186" s="17" t="s">
-        <v>856</v>
+        <v>864</v>
       </c>
       <c r="B186" s="16" t="s">
-        <v>857</v>
+        <v>865</v>
       </c>
       <c r="C186" s="19"/>
     </row>
     <row r="187" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A187" s="17" t="s">
-        <v>858</v>
+        <v>866</v>
       </c>
       <c r="B187" s="16" t="s">
-        <v>859</v>
+        <v>867</v>
       </c>
       <c r="C187" s="19"/>
     </row>
     <row r="189" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A189" s="24" t="s">
-        <v>860</v>
-      </c>
-      <c r="B189" s="25"/>
-      <c r="C189" s="25"/>
+      <c r="A189" s="27" t="s">
+        <v>868</v>
+      </c>
+      <c r="B189" s="28"/>
+      <c r="C189" s="28"/>
     </row>
     <row r="190" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A190" s="17" t="s">
-        <v>861</v>
+        <v>869</v>
       </c>
       <c r="B190" s="16" t="s">
-        <v>862</v>
+        <v>870</v>
       </c>
       <c r="C190" s="19"/>
     </row>
     <row r="191" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A191" s="17" t="s">
-        <v>863</v>
+        <v>871</v>
       </c>
       <c r="B191" s="16" t="s">
-        <v>864</v>
+        <v>872</v>
       </c>
       <c r="C191" s="19"/>
     </row>
     <row r="192" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A192" s="17" t="s">
-        <v>865</v>
+        <v>873</v>
       </c>
       <c r="B192" s="16" t="s">
-        <v>866</v>
+        <v>874</v>
       </c>
       <c r="C192" s="19"/>
     </row>
     <row r="193" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A193" s="17" t="s">
-        <v>867</v>
+        <v>875</v>
       </c>
       <c r="B193" s="16" t="s">
-        <v>868</v>
+        <v>876</v>
       </c>
       <c r="C193" s="19"/>
     </row>
     <row r="194" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A194" s="17" t="s">
-        <v>869</v>
+        <v>877</v>
       </c>
       <c r="B194" s="16" t="s">
-        <v>870</v>
+        <v>878</v>
       </c>
       <c r="C194" s="19"/>
     </row>
     <row r="195" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="196" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A196" s="24" t="s">
-        <v>871</v>
-      </c>
-      <c r="B196" s="25"/>
-      <c r="C196" s="25"/>
+      <c r="A196" s="27" t="s">
+        <v>879</v>
+      </c>
+      <c r="B196" s="28"/>
+      <c r="C196" s="28"/>
     </row>
     <row r="197" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A197" s="17" t="s">
-        <v>872</v>
+        <v>880</v>
       </c>
       <c r="B197" s="16" t="s">
-        <v>873</v>
+        <v>881</v>
       </c>
       <c r="C197" s="19"/>
     </row>
     <row r="198" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A198" s="17" t="s">
-        <v>874</v>
+        <v>882</v>
       </c>
       <c r="B198" s="16" t="s">
-        <v>875</v>
+        <v>883</v>
       </c>
       <c r="C198" s="19"/>
     </row>
     <row r="199" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A199" s="17" t="s">
-        <v>876</v>
+        <v>884</v>
       </c>
       <c r="B199" s="16" t="s">
-        <v>877</v>
+        <v>885</v>
       </c>
       <c r="C199" s="19"/>
     </row>
     <row r="200" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A200" s="17" t="s">
-        <v>878</v>
+        <v>886</v>
       </c>
       <c r="B200" s="16" t="s">
-        <v>879</v>
+        <v>887</v>
       </c>
       <c r="C200" s="19"/>
     </row>
     <row r="201" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A201" s="17" t="s">
-        <v>880</v>
+        <v>888</v>
       </c>
       <c r="B201" s="16" t="s">
-        <v>881</v>
+        <v>889</v>
       </c>
       <c r="C201" s="19"/>
     </row>
     <row r="202" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A202" s="24" t="s">
-        <v>882</v>
-      </c>
-      <c r="B202" s="25"/>
-      <c r="C202" s="25"/>
+      <c r="A202" s="27" t="s">
+        <v>890</v>
+      </c>
+      <c r="B202" s="28"/>
+      <c r="C202" s="28"/>
     </row>
     <row r="203" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A203" s="17" t="s">
-        <v>883</v>
+        <v>891</v>
       </c>
       <c r="B203" s="16" t="s">
-        <v>884</v>
+        <v>892</v>
       </c>
       <c r="C203" s="19"/>
     </row>
     <row r="204" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A204" s="17" t="s">
-        <v>885</v>
+        <v>893</v>
       </c>
       <c r="B204" s="16" t="s">
-        <v>886</v>
+        <v>894</v>
       </c>
       <c r="C204" s="19"/>
     </row>
     <row r="205" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A205" s="17" t="s">
-        <v>887</v>
+        <v>895</v>
       </c>
       <c r="B205" s="16" t="s">
-        <v>888</v>
+        <v>896</v>
       </c>
       <c r="C205" s="19"/>
     </row>
     <row r="206" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A206" s="17" t="s">
-        <v>889</v>
+        <v>897</v>
       </c>
       <c r="B206" s="16" t="s">
-        <v>890</v>
+        <v>898</v>
       </c>
       <c r="C206" s="19"/>
     </row>
     <row r="207" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="208" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A208" s="24" t="s">
-        <v>891</v>
-      </c>
-      <c r="B208" s="25"/>
-      <c r="C208" s="25"/>
+      <c r="A208" s="27" t="s">
+        <v>899</v>
+      </c>
+      <c r="B208" s="28"/>
+      <c r="C208" s="28"/>
     </row>
     <row r="209" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A209" s="17" t="s">
-        <v>892</v>
+        <v>900</v>
       </c>
       <c r="B209" s="16" t="s">
-        <v>893</v>
+        <v>901</v>
       </c>
       <c r="C209" s="19"/>
     </row>
     <row r="210" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A210" s="17" t="s">
-        <v>894</v>
+        <v>902</v>
       </c>
       <c r="B210" s="16" t="s">
-        <v>895</v>
+        <v>903</v>
       </c>
       <c r="C210" s="19"/>
     </row>
     <row r="211" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A211" s="17" t="s">
-        <v>896</v>
+        <v>904</v>
       </c>
       <c r="B211" s="16" t="s">
-        <v>897</v>
+        <v>905</v>
       </c>
       <c r="C211" s="19"/>
     </row>
     <row r="212" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A212" s="17" t="s">
-        <v>898</v>
+        <v>906</v>
       </c>
       <c r="B212" s="16" t="s">
-        <v>899</v>
+        <v>907</v>
       </c>
       <c r="C212" s="19"/>
     </row>
     <row r="213" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="214" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A214" s="24" t="s">
-        <v>900</v>
-      </c>
-      <c r="B214" s="25"/>
-      <c r="C214" s="25"/>
+      <c r="A214" s="27" t="s">
+        <v>908</v>
+      </c>
+      <c r="B214" s="28"/>
+      <c r="C214" s="28"/>
     </row>
     <row r="215" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A215" s="17" t="s">
-        <v>901</v>
+        <v>909</v>
       </c>
       <c r="B215" s="16" t="s">
-        <v>902</v>
+        <v>910</v>
       </c>
       <c r="C215" s="19"/>
     </row>
     <row r="216" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A216" s="17" t="s">
-        <v>903</v>
+        <v>911</v>
       </c>
       <c r="B216" s="16" t="s">
-        <v>904</v>
+        <v>912</v>
       </c>
       <c r="C216" s="19"/>
     </row>
     <row r="217" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A217" s="17" t="s">
-        <v>905</v>
+        <v>913</v>
       </c>
       <c r="B217" s="16" t="s">
-        <v>906</v>
+        <v>914</v>
       </c>
       <c r="C217" s="19"/>
     </row>
     <row r="218" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A218" s="17" t="s">
-        <v>907</v>
+        <v>915</v>
       </c>
       <c r="B218" s="16" t="s">
-        <v>908</v>
+        <v>916</v>
       </c>
       <c r="C218" s="19"/>
     </row>
     <row r="219" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="220" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A220" s="24" t="s">
-        <v>909</v>
-      </c>
-      <c r="B220" s="25"/>
-      <c r="C220" s="25"/>
+      <c r="A220" s="27" t="s">
+        <v>917</v>
+      </c>
+      <c r="B220" s="28"/>
+      <c r="C220" s="28"/>
     </row>
     <row r="221" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A221" s="17" t="s">
-        <v>910</v>
+        <v>918</v>
       </c>
       <c r="B221" s="16" t="s">
-        <v>911</v>
+        <v>919</v>
       </c>
       <c r="C221" s="19"/>
     </row>
     <row r="222" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A222" s="17" t="s">
-        <v>912</v>
+        <v>920</v>
       </c>
       <c r="B222" s="16" t="s">
-        <v>913</v>
+        <v>921</v>
       </c>
       <c r="C222" s="19"/>
     </row>
     <row r="223" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="224" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A224" s="24" t="s">
-        <v>914</v>
-      </c>
-      <c r="B224" s="25"/>
-      <c r="C224" s="25"/>
+      <c r="A224" s="27" t="s">
+        <v>922</v>
+      </c>
+      <c r="B224" s="28"/>
+      <c r="C224" s="28"/>
     </row>
     <row r="225" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A225" s="17" t="s">
-        <v>915</v>
+        <v>923</v>
       </c>
       <c r="B225" s="16" t="s">
-        <v>916</v>
+        <v>924</v>
       </c>
       <c r="C225" s="19"/>
     </row>
     <row r="226" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A226" s="17" t="s">
-        <v>917</v>
+        <v>925</v>
       </c>
       <c r="B226" s="16" t="s">
-        <v>918</v>
+        <v>926</v>
       </c>
       <c r="C226" s="19"/>
     </row>
     <row r="227" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A227" s="17" t="s">
-        <v>919</v>
+        <v>927</v>
       </c>
       <c r="B227" s="16" t="s">
-        <v>920</v>
+        <v>928</v>
       </c>
       <c r="C227" s="19"/>
     </row>
     <row r="228" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A228" s="17" t="s">
-        <v>921</v>
+        <v>929</v>
       </c>
       <c r="B228" s="16" t="s">
-        <v>922</v>
+        <v>930</v>
       </c>
       <c r="C228" s="19"/>
     </row>
     <row r="229" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="230" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A230" s="24" t="s">
-        <v>923</v>
-      </c>
-      <c r="B230" s="25"/>
-      <c r="C230" s="25"/>
+      <c r="A230" s="27" t="s">
+        <v>931</v>
+      </c>
+      <c r="B230" s="28"/>
+      <c r="C230" s="28"/>
     </row>
     <row r="231" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A231" s="17" t="s">
-        <v>924</v>
+        <v>932</v>
       </c>
       <c r="B231" s="16" t="s">
-        <v>925</v>
+        <v>933</v>
       </c>
       <c r="C231" s="19"/>
     </row>
     <row r="232" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A232" s="17" t="s">
-        <v>926</v>
+        <v>934</v>
       </c>
       <c r="B232" s="16" t="s">
-        <v>927</v>
+        <v>935</v>
       </c>
       <c r="C232" s="19"/>
     </row>
     <row r="233" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A233" s="17" t="s">
-        <v>928</v>
+        <v>936</v>
       </c>
       <c r="B233" s="16" t="s">
-        <v>929</v>
+        <v>937</v>
       </c>
       <c r="C233" s="19"/>
     </row>
     <row r="234" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A234" s="17" t="s">
-        <v>930</v>
+        <v>938</v>
       </c>
       <c r="B234" s="16" t="s">
-        <v>931</v>
+        <v>939</v>
       </c>
       <c r="C234" s="19"/>
     </row>
     <row r="235" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="236" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="237" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A237" s="24" t="s">
-        <v>932</v>
-      </c>
-      <c r="B237" s="25"/>
-      <c r="C237" s="25"/>
+      <c r="A237" s="27" t="s">
+        <v>940</v>
+      </c>
+      <c r="B237" s="28"/>
+      <c r="C237" s="28"/>
     </row>
     <row r="238" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A238" s="17" t="s">
-        <v>758</v>
+        <v>766</v>
       </c>
       <c r="B238" s="16" t="s">
-        <v>933</v>
+        <v>941</v>
       </c>
       <c r="C238" s="19"/>
     </row>
     <row r="239" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A239" s="17" t="s">
-        <v>934</v>
+        <v>942</v>
       </c>
       <c r="B239" s="16" t="s">
-        <v>935</v>
+        <v>943</v>
       </c>
       <c r="C239" s="19"/>
     </row>
     <row r="240" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A240" s="17" t="s">
-        <v>936</v>
+        <v>944</v>
       </c>
       <c r="B240" s="16" t="s">
-        <v>937</v>
+        <v>945</v>
       </c>
       <c r="C240" s="19"/>
     </row>
     <row r="241" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A241" s="17" t="s">
-        <v>938</v>
+        <v>946</v>
       </c>
       <c r="B241" s="16" t="s">
-        <v>939</v>
+        <v>947</v>
       </c>
       <c r="C241" s="19"/>
     </row>
     <row r="242" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A242" s="17" t="s">
-        <v>940</v>
+        <v>948</v>
       </c>
       <c r="B242" s="16" t="s">
-        <v>941</v>
+        <v>949</v>
       </c>
       <c r="C242" s="19"/>
     </row>
     <row r="243" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A243" s="17" t="s">
-        <v>942</v>
+        <v>950</v>
       </c>
       <c r="B243" s="16" t="s">
-        <v>943</v>
+        <v>951</v>
       </c>
       <c r="C243" s="19"/>
     </row>
     <row r="245" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A245" s="24" t="s">
-        <v>944</v>
-      </c>
-      <c r="B245" s="25"/>
-      <c r="C245" s="25"/>
+      <c r="A245" s="27" t="s">
+        <v>952</v>
+      </c>
+      <c r="B245" s="28"/>
+      <c r="C245" s="28"/>
     </row>
     <row r="246" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A246" s="17" t="s">
-        <v>945</v>
+        <v>953</v>
       </c>
       <c r="B246" s="16" t="s">
-        <v>946</v>
+        <v>954</v>
       </c>
       <c r="C246" s="19"/>
     </row>
     <row r="247" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A247" s="17" t="s">
-        <v>912</v>
+        <v>920</v>
       </c>
       <c r="B247" s="16" t="s">
-        <v>947</v>
+        <v>955</v>
       </c>
       <c r="C247" s="19"/>
     </row>
     <row r="248" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A248" s="17" t="s">
-        <v>948</v>
+        <v>956</v>
       </c>
       <c r="B248" s="16" t="s">
-        <v>949</v>
+        <v>957</v>
       </c>
       <c r="C248" s="19"/>
     </row>
     <row r="249" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A249" s="17" t="s">
-        <v>950</v>
+        <v>958</v>
       </c>
       <c r="B249" s="16" t="s">
-        <v>951</v>
+        <v>959</v>
       </c>
       <c r="C249" s="19"/>
     </row>
     <row r="250" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="251" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="252" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A252" s="24" t="s">
-        <v>952</v>
-      </c>
-      <c r="B252" s="25"/>
-      <c r="C252" s="25"/>
+      <c r="A252" s="27" t="s">
+        <v>960</v>
+      </c>
+      <c r="B252" s="28"/>
+      <c r="C252" s="28"/>
     </row>
     <row r="253" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A253" s="17" t="s">
-        <v>953</v>
+        <v>961</v>
       </c>
       <c r="B253" s="16" t="s">
-        <v>954</v>
+        <v>962</v>
       </c>
       <c r="C253" s="19"/>
     </row>
     <row r="254" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A254" s="17" t="s">
-        <v>955</v>
+        <v>963</v>
       </c>
       <c r="B254" s="16" t="s">
-        <v>956</v>
+        <v>964</v>
       </c>
       <c r="C254" s="19"/>
     </row>
     <row r="255" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A255" s="17" t="s">
-        <v>957</v>
+        <v>965</v>
       </c>
       <c r="B255" s="16" t="s">
-        <v>958</v>
+        <v>966</v>
       </c>
       <c r="C255" s="19"/>
     </row>
     <row r="256" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A256" s="17" t="s">
-        <v>959</v>
+        <v>967</v>
       </c>
       <c r="B256" s="16" t="s">
-        <v>960</v>
+        <v>968</v>
       </c>
       <c r="C256" s="19"/>
     </row>
     <row r="257" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A257" s="17" t="s">
-        <v>961</v>
+        <v>969</v>
       </c>
       <c r="B257" s="16" t="s">
-        <v>962</v>
+        <v>970</v>
       </c>
       <c r="C257" s="19"/>
     </row>
     <row r="258" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A258" s="17" t="s">
-        <v>963</v>
+        <v>971</v>
       </c>
       <c r="B258" s="16" t="s">
-        <v>964</v>
+        <v>972</v>
       </c>
       <c r="C258" s="19"/>
     </row>
     <row r="259" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A259" s="24" t="s">
-        <v>965</v>
-      </c>
-      <c r="B259" s="25"/>
-      <c r="C259" s="25"/>
+      <c r="A259" s="27" t="s">
+        <v>973</v>
+      </c>
+      <c r="B259" s="28"/>
+      <c r="C259" s="28"/>
     </row>
     <row r="260" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A260" s="17" t="s">
-        <v>966</v>
+        <v>974</v>
       </c>
       <c r="B260" s="16" t="s">
-        <v>967</v>
+        <v>975</v>
       </c>
       <c r="C260" s="19"/>
     </row>
     <row r="261" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A261" s="17" t="s">
-        <v>968</v>
+        <v>976</v>
       </c>
       <c r="B261" s="16" t="s">
-        <v>969</v>
+        <v>977</v>
       </c>
       <c r="C261" s="19"/>
     </row>
     <row r="262" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A262" s="17" t="s">
-        <v>970</v>
+        <v>978</v>
       </c>
       <c r="B262" s="16" t="s">
-        <v>971</v>
+        <v>979</v>
       </c>
       <c r="C262" s="19"/>
     </row>
     <row r="263" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A263" s="17" t="s">
-        <v>972</v>
+        <v>980</v>
       </c>
       <c r="B263" s="16" t="s">
-        <v>973</v>
+        <v>981</v>
       </c>
       <c r="C263" s="19"/>
     </row>
     <row r="264" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="265" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A265" s="24" t="s">
-        <v>974</v>
-      </c>
-      <c r="B265" s="25"/>
-      <c r="C265" s="25"/>
+      <c r="A265" s="27" t="s">
+        <v>982</v>
+      </c>
+      <c r="B265" s="28"/>
+      <c r="C265" s="28"/>
     </row>
     <row r="266" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A266" s="17" t="s">
-        <v>975</v>
+        <v>983</v>
       </c>
       <c r="B266" s="16" t="s">
-        <v>976</v>
+        <v>984</v>
       </c>
       <c r="C266" s="19"/>
     </row>
     <row r="267" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A267" s="17" t="s">
-        <v>977</v>
+        <v>985</v>
       </c>
       <c r="B267" s="16" t="s">
-        <v>978</v>
+        <v>986</v>
       </c>
       <c r="C267" s="19"/>
     </row>
     <row r="268" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A268" s="17" t="s">
-        <v>979</v>
+        <v>987</v>
       </c>
       <c r="B268" s="16" t="s">
-        <v>980</v>
+        <v>988</v>
       </c>
       <c r="C268" s="19"/>
     </row>
     <row r="269" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A269" s="17" t="s">
-        <v>981</v>
+        <v>989</v>
       </c>
       <c r="B269" s="16" t="s">
-        <v>982</v>
+        <v>990</v>
       </c>
       <c r="C269" s="19"/>
     </row>
     <row r="270" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="271" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A271" s="24" t="s">
-        <v>983</v>
-      </c>
-      <c r="B271" s="25"/>
-      <c r="C271" s="25"/>
+      <c r="A271" s="27" t="s">
+        <v>991</v>
+      </c>
+      <c r="B271" s="28"/>
+      <c r="C271" s="28"/>
     </row>
     <row r="272" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A272" s="17" t="s">
-        <v>984</v>
+        <v>992</v>
       </c>
       <c r="B272" s="16" t="s">
-        <v>985</v>
+        <v>993</v>
       </c>
       <c r="C272" s="19"/>
     </row>
     <row r="273" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A273" s="17" t="s">
-        <v>986</v>
+        <v>994</v>
       </c>
       <c r="B273" s="16" t="s">
-        <v>987</v>
+        <v>995</v>
       </c>
       <c r="C273" s="19"/>
     </row>
     <row r="274" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="275" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A275" s="24" t="s">
-        <v>988</v>
-      </c>
-      <c r="B275" s="25"/>
-      <c r="C275" s="25"/>
+      <c r="A275" s="27" t="s">
+        <v>996</v>
+      </c>
+      <c r="B275" s="28"/>
+      <c r="C275" s="28"/>
     </row>
     <row r="276" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A276" s="17" t="s">
-        <v>989</v>
+        <v>997</v>
       </c>
       <c r="B276" s="16" t="s">
-        <v>990</v>
+        <v>998</v>
       </c>
       <c r="C276" s="19"/>
     </row>
     <row r="277" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A277" s="17" t="s">
-        <v>991</v>
+        <v>999</v>
       </c>
       <c r="B277" s="16" t="s">
-        <v>992</v>
+        <v>1000</v>
       </c>
       <c r="C277" s="19"/>
     </row>
     <row r="278" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A278" s="17" t="s">
-        <v>993</v>
+        <v>1001</v>
       </c>
       <c r="B278" s="16" t="s">
-        <v>994</v>
+        <v>1002</v>
       </c>
       <c r="C278" s="19"/>
     </row>
     <row r="279" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="280" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A280" s="24" t="s">
-        <v>995</v>
-      </c>
-      <c r="B280" s="25"/>
-      <c r="C280" s="25"/>
+      <c r="A280" s="27" t="s">
+        <v>1003</v>
+      </c>
+      <c r="B280" s="28"/>
+      <c r="C280" s="28"/>
     </row>
     <row r="281" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A281" s="17" t="s">
-        <v>996</v>
+        <v>1004</v>
       </c>
       <c r="B281" s="16" t="s">
-        <v>997</v>
+        <v>1005</v>
       </c>
       <c r="C281" s="19"/>
     </row>
     <row r="282" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A282" s="17" t="s">
-        <v>998</v>
+        <v>1006</v>
       </c>
       <c r="B282" s="16" t="s">
-        <v>999</v>
+        <v>1007</v>
       </c>
       <c r="C282" s="19"/>
     </row>
     <row r="283" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A283" s="17" t="s">
-        <v>1000</v>
+        <v>1008</v>
       </c>
       <c r="B283" s="16" t="s">
-        <v>1001</v>
+        <v>1009</v>
       </c>
       <c r="C283" s="19"/>
     </row>
     <row r="284" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A284" s="24" t="s">
-        <v>1002</v>
-      </c>
-      <c r="B284" s="25"/>
-      <c r="C284" s="25"/>
+      <c r="A284" s="27" t="s">
+        <v>1010</v>
+      </c>
+      <c r="B284" s="28"/>
+      <c r="C284" s="28"/>
     </row>
     <row r="285" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A285" s="17" t="s">
-        <v>1003</v>
+        <v>1011</v>
       </c>
       <c r="B285" s="16" t="s">
-        <v>1004</v>
+        <v>1012</v>
       </c>
       <c r="C285" s="19"/>
     </row>
     <row r="286" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="287" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A287" s="24" t="s">
-        <v>1005</v>
-      </c>
-      <c r="B287" s="25"/>
-      <c r="C287" s="25"/>
+      <c r="A287" s="27" t="s">
+        <v>1013</v>
+      </c>
+      <c r="B287" s="28"/>
+      <c r="C287" s="28"/>
     </row>
     <row r="288" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A288" s="17" t="s">
-        <v>1006</v>
+        <v>1014</v>
       </c>
       <c r="B288" s="16" t="s">
-        <v>1007</v>
+        <v>1015</v>
       </c>
       <c r="C288" s="19"/>
     </row>
     <row r="289" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A289" s="17" t="s">
-        <v>1008</v>
+        <v>1016</v>
       </c>
       <c r="B289" s="16" t="s">
-        <v>1009</v>
+        <v>1017</v>
       </c>
       <c r="C289" s="19"/>
     </row>
     <row r="290" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A290" s="17" t="s">
-        <v>1010</v>
+        <v>1018</v>
       </c>
       <c r="B290" s="16" t="s">
-        <v>1011</v>
+        <v>1019</v>
       </c>
       <c r="C290" s="19"/>
     </row>
     <row r="291" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A291" s="17" t="s">
-        <v>1012</v>
+        <v>1020</v>
       </c>
       <c r="B291" s="16" t="s">
-        <v>1013</v>
+        <v>1021</v>
       </c>
       <c r="C291" s="19"/>
     </row>
     <row r="292" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A292" s="24" t="s">
-        <v>1014</v>
-      </c>
-      <c r="B292" s="25"/>
-      <c r="C292" s="25"/>
+      <c r="A292" s="27" t="s">
+        <v>1022</v>
+      </c>
+      <c r="B292" s="28"/>
+      <c r="C292" s="28"/>
     </row>
     <row r="293" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A293" s="17" t="s">
-        <v>1015</v>
+        <v>1023</v>
       </c>
       <c r="B293" s="16" t="s">
-        <v>1016</v>
+        <v>1024</v>
       </c>
       <c r="C293" s="19"/>
     </row>
     <row r="294" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="295" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A295" s="24" t="s">
-        <v>1017</v>
-      </c>
-      <c r="B295" s="25"/>
-      <c r="C295" s="25"/>
+      <c r="A295" s="27" t="s">
+        <v>1025</v>
+      </c>
+      <c r="B295" s="28"/>
+      <c r="C295" s="28"/>
     </row>
     <row r="296" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A296" s="17" t="s">
-        <v>1018</v>
+        <v>1026</v>
       </c>
       <c r="B296" s="16" t="s">
-        <v>1019</v>
+        <v>1027</v>
       </c>
       <c r="C296" s="19"/>
     </row>
     <row r="297" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A297" s="17" t="s">
-        <v>1020</v>
+        <v>1028</v>
       </c>
       <c r="B297" s="16" t="s">
-        <v>1021</v>
+        <v>1029</v>
       </c>
       <c r="C297" s="19"/>
     </row>
     <row r="298" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A298" s="17" t="s">
-        <v>1022</v>
+        <v>1030</v>
       </c>
       <c r="B298" s="16" t="s">
-        <v>1023</v>
+        <v>1031</v>
       </c>
       <c r="C298" s="19"/>
     </row>
     <row r="299" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="300" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A300" s="24" t="s">
-        <v>1024</v>
-      </c>
-      <c r="B300" s="25"/>
-      <c r="C300" s="25"/>
+      <c r="A300" s="27" t="s">
+        <v>1032</v>
+      </c>
+      <c r="B300" s="28"/>
+      <c r="C300" s="28"/>
     </row>
     <row r="301" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A301" s="17" t="s">
-        <v>1025</v>
+        <v>1033</v>
       </c>
       <c r="B301" s="16" t="s">
-        <v>1026</v>
+        <v>1034</v>
       </c>
       <c r="C301" s="19"/>
     </row>
     <row r="302" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A302" s="17" t="s">
-        <v>1027</v>
+        <v>1035</v>
       </c>
       <c r="B302" s="16" t="s">
-        <v>1028</v>
+        <v>1036</v>
       </c>
       <c r="C302" s="19"/>
     </row>
     <row r="303" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A303" s="17" t="s">
-        <v>1029</v>
+        <v>1037</v>
       </c>
       <c r="B303" s="16" t="s">
-        <v>1030</v>
+        <v>1038</v>
       </c>
       <c r="C303" s="19"/>
     </row>
     <row r="304" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A304" s="17" t="s">
-        <v>1031</v>
+        <v>1039</v>
       </c>
       <c r="B304" s="16" t="s">
-        <v>1032</v>
+        <v>1040</v>
       </c>
       <c r="C304" s="19"/>
     </row>
     <row r="305" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A305" s="17" t="s">
-        <v>1033</v>
+        <v>1041</v>
       </c>
       <c r="B305" s="16" t="s">
-        <v>1034</v>
+        <v>1042</v>
       </c>
       <c r="C305" s="19"/>
     </row>
     <row r="306" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A306" s="17" t="s">
-        <v>1035</v>
+        <v>1043</v>
       </c>
       <c r="B306" s="16" t="s">
-        <v>1036</v>
+        <v>1044</v>
       </c>
       <c r="C306" s="19"/>
     </row>
     <row r="307" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A307" s="17" t="s">
-        <v>1037</v>
+        <v>1045</v>
       </c>
       <c r="B307" s="16" t="s">
-        <v>1038</v>
+        <v>1046</v>
       </c>
       <c r="C307" s="19"/>
     </row>
     <row r="308" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A308" s="24" t="s">
-        <v>1039</v>
-      </c>
-      <c r="B308" s="25"/>
-      <c r="C308" s="25"/>
+      <c r="A308" s="27" t="s">
+        <v>1047</v>
+      </c>
+      <c r="B308" s="28"/>
+      <c r="C308" s="28"/>
     </row>
     <row r="309" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A309" s="17" t="s">
-        <v>1040</v>
+        <v>1048</v>
       </c>
       <c r="B309" s="16" t="s">
-        <v>1041</v>
+        <v>1049</v>
       </c>
       <c r="C309" s="19"/>
     </row>
     <row r="310" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A310" s="17" t="s">
-        <v>1042</v>
+        <v>1050</v>
       </c>
       <c r="B310" s="16" t="s">
-        <v>1043</v>
+        <v>1051</v>
       </c>
       <c r="C310" s="19"/>
     </row>
     <row r="311" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A311" s="17" t="s">
-        <v>1044</v>
+        <v>1052</v>
       </c>
       <c r="B311" s="16" t="s">
-        <v>1045</v>
+        <v>1053</v>
       </c>
       <c r="C311" s="19"/>
     </row>
     <row r="312" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A312" s="17" t="s">
-        <v>1046</v>
+        <v>1054</v>
       </c>
       <c r="B312" s="16" t="s">
-        <v>1047</v>
+        <v>1055</v>
       </c>
       <c r="C312" s="19"/>
     </row>
     <row r="313" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A313" s="24" t="s">
-        <v>1048</v>
-      </c>
-      <c r="B313" s="25"/>
-      <c r="C313" s="25"/>
+      <c r="A313" s="27" t="s">
+        <v>1056</v>
+      </c>
+      <c r="B313" s="28"/>
+      <c r="C313" s="28"/>
     </row>
     <row r="314" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A314" s="17" t="s">
-        <v>1049</v>
+        <v>1057</v>
       </c>
       <c r="B314" s="16" t="s">
-        <v>1050</v>
+        <v>1058</v>
       </c>
       <c r="C314" s="19"/>
     </row>
     <row r="315" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A315" s="17" t="s">
-        <v>1051</v>
+        <v>1059</v>
       </c>
       <c r="B315" s="16" t="s">
-        <v>1052</v>
+        <v>1060</v>
       </c>
       <c r="C315" s="19"/>
     </row>
     <row r="316" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="317" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="318" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A318" s="24" t="s">
-        <v>1053</v>
-      </c>
-      <c r="B318" s="25"/>
-      <c r="C318" s="25"/>
+      <c r="A318" s="27" t="s">
+        <v>1061</v>
+      </c>
+      <c r="B318" s="28"/>
+      <c r="C318" s="28"/>
     </row>
     <row r="319" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A319" s="17" t="s">
-        <v>1054</v>
+        <v>1062</v>
       </c>
       <c r="B319" s="16" t="s">
-        <v>1055</v>
+        <v>1063</v>
       </c>
       <c r="C319" s="19"/>
     </row>
     <row r="320" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A320" s="17" t="s">
-        <v>1056</v>
+        <v>1064</v>
       </c>
       <c r="B320" s="16" t="s">
-        <v>1057</v>
+        <v>1065</v>
       </c>
       <c r="C320" s="19"/>
     </row>
     <row r="321" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A321" s="17" t="s">
-        <v>1058</v>
+        <v>1066</v>
       </c>
       <c r="B321" s="16" t="s">
-        <v>1059</v>
+        <v>1067</v>
       </c>
       <c r="C321" s="19"/>
     </row>
     <row r="322" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A322" s="17" t="s">
-        <v>1060</v>
+        <v>1068</v>
       </c>
       <c r="B322" s="16" t="s">
-        <v>1061</v>
+        <v>1069</v>
       </c>
       <c r="C322" s="19"/>
     </row>
     <row r="323" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A323" s="17" t="s">
-        <v>1062</v>
+        <v>1070</v>
       </c>
       <c r="B323" s="16" t="s">
-        <v>1063</v>
+        <v>1071</v>
       </c>
       <c r="C323" s="19"/>
     </row>
     <row r="324" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A324" s="17" t="s">
-        <v>1064</v>
+        <v>1072</v>
       </c>
       <c r="B324" s="16" t="s">
-        <v>1065</v>
+        <v>1073</v>
       </c>
       <c r="C324" s="19"/>
     </row>
     <row r="326" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A326" s="26" t="s">
-        <v>1066</v>
-      </c>
-      <c r="B326" s="27"/>
-      <c r="C326" s="27"/>
+      <c r="A326" s="29" t="s">
+        <v>1074</v>
+      </c>
+      <c r="B326" s="30"/>
+      <c r="C326" s="30"/>
     </row>
     <row r="327" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A327" s="17" t="s">
-        <v>1067</v>
+        <v>1075</v>
       </c>
       <c r="B327" s="16" t="s">
-        <v>1068</v>
+        <v>1076</v>
       </c>
       <c r="C327" s="19"/>
     </row>
     <row r="328" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A328" s="17" t="s">
-        <v>1069</v>
+        <v>1077</v>
       </c>
       <c r="B328" s="16" t="s">
-        <v>1070</v>
+        <v>1078</v>
       </c>
       <c r="C328" s="19"/>
     </row>
     <row r="329" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A329" s="17" t="s">
-        <v>1071</v>
+        <v>1079</v>
       </c>
       <c r="B329" s="16" t="s">
-        <v>1072</v>
+        <v>1080</v>
       </c>
       <c r="C329" s="19"/>
     </row>
     <row r="330" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A330" s="17" t="s">
-        <v>1073</v>
+        <v>1081</v>
       </c>
       <c r="B330" s="16" t="s">
-        <v>1074</v>
+        <v>1082</v>
       </c>
       <c r="C330" s="19"/>
     </row>
     <row r="331" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A331" s="17" t="s">
-        <v>1075</v>
+        <v>1083</v>
       </c>
       <c r="B331" s="16" t="s">
-        <v>1076</v>
+        <v>1084</v>
       </c>
       <c r="C331" s="19"/>
     </row>
     <row r="332" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A332" s="17" t="s">
-        <v>1077</v>
+        <v>1085</v>
       </c>
       <c r="B332" s="16" t="s">
-        <v>1078</v>
+        <v>1086</v>
       </c>
       <c r="C332" s="19"/>
     </row>
     <row r="333" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A333" s="17" t="s">
-        <v>1079</v>
+        <v>1087</v>
       </c>
       <c r="B333" s="16" t="s">
-        <v>1080</v>
+        <v>1088</v>
       </c>
       <c r="C333" s="19"/>
     </row>
     <row r="334" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A334" s="17" t="s">
-        <v>1081</v>
+        <v>1089</v>
       </c>
       <c r="B334" s="16" t="s">
-        <v>1082</v>
+        <v>1090</v>
       </c>
       <c r="C334" s="19"/>
     </row>
     <row r="335" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A335" s="26" t="s">
-        <v>1083</v>
-      </c>
-      <c r="B335" s="27"/>
-      <c r="C335" s="27"/>
+      <c r="A335" s="29" t="s">
+        <v>1091</v>
+      </c>
+      <c r="B335" s="30"/>
+      <c r="C335" s="30"/>
     </row>
     <row r="336" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A336" s="17" t="s">
-        <v>1084</v>
+        <v>1092</v>
       </c>
       <c r="B336" s="16" t="s">
-        <v>1085</v>
+        <v>1093</v>
       </c>
       <c r="C336" s="19"/>
     </row>
     <row r="337" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A337" s="17" t="s">
-        <v>1086</v>
+        <v>1094</v>
       </c>
       <c r="B337" s="16" t="s">
-        <v>1087</v>
+        <v>1095</v>
       </c>
       <c r="C337" s="19"/>
     </row>
     <row r="338" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A338" s="17" t="s">
-        <v>1088</v>
+        <v>1096</v>
       </c>
       <c r="B338" s="16" t="s">
-        <v>1089</v>
+        <v>1097</v>
       </c>
       <c r="C338" s="19"/>
     </row>
     <row r="339" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A339" s="17" t="s">
-        <v>1090</v>
+        <v>1098</v>
       </c>
       <c r="B339" s="16" t="s">
-        <v>1091</v>
+        <v>1099</v>
       </c>
       <c r="C339" s="19"/>
     </row>
     <row r="340" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A340" s="17" t="s">
-        <v>1092</v>
+        <v>1100</v>
       </c>
       <c r="B340" s="16" t="s">
-        <v>1093</v>
+        <v>1101</v>
       </c>
       <c r="C340" s="19"/>
     </row>
     <row r="341" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A341" s="17" t="s">
-        <v>1094</v>
+        <v>1102</v>
       </c>
       <c r="B341" s="16" t="s">
-        <v>1095</v>
+        <v>1103</v>
       </c>
       <c r="C341" s="19"/>
     </row>
     <row r="342" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A342" s="17" t="s">
-        <v>1096</v>
+        <v>1104</v>
       </c>
       <c r="B342" s="16" t="s">
-        <v>1097</v>
+        <v>1105</v>
       </c>
       <c r="C342" s="19"/>
     </row>
     <row r="343" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A343" s="17" t="s">
-        <v>1098</v>
+        <v>1106</v>
       </c>
       <c r="B343" s="16" t="s">
-        <v>1099</v>
+        <v>1107</v>
       </c>
       <c r="C343" s="19"/>
     </row>
     <row r="344" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A344" s="17" t="s">
-        <v>1100</v>
+        <v>1108</v>
       </c>
       <c r="B344" s="16" t="s">
-        <v>1101</v>
+        <v>1109</v>
       </c>
       <c r="C344" s="19"/>
     </row>
     <row r="345" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A345" s="17" t="s">
-        <v>1102</v>
+        <v>1110</v>
       </c>
       <c r="B345" s="16" t="s">
-        <v>1103</v>
+        <v>1111</v>
       </c>
       <c r="C345" s="19"/>
     </row>
     <row r="347" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A347" s="24" t="s">
-        <v>1104</v>
-      </c>
-      <c r="B347" s="25"/>
-      <c r="C347" s="25"/>
+      <c r="A347" s="27" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B347" s="28"/>
+      <c r="C347" s="28"/>
     </row>
     <row r="348" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A348" s="17" t="s">
-        <v>1105</v>
+        <v>1113</v>
       </c>
       <c r="B348" s="16" t="s">
-        <v>1106</v>
+        <v>1114</v>
       </c>
       <c r="C348" s="19"/>
     </row>
     <row r="349" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A349" s="17" t="s">
-        <v>1107</v>
+        <v>1115</v>
       </c>
       <c r="B349" s="16" t="s">
-        <v>1108</v>
+        <v>1116</v>
       </c>
       <c r="C349" s="19"/>
     </row>
     <row r="350" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A350" s="17" t="s">
-        <v>1109</v>
+        <v>1117</v>
       </c>
       <c r="B350" s="16" t="s">
-        <v>1110</v>
+        <v>1118</v>
       </c>
       <c r="C350" s="19"/>
     </row>
     <row r="351" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A351" s="17" t="s">
-        <v>1111</v>
+        <v>1119</v>
       </c>
       <c r="B351" s="16" t="s">
-        <v>1112</v>
+        <v>1120</v>
       </c>
       <c r="C351" s="19"/>
     </row>
     <row r="352" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A352" s="17" t="s">
-        <v>1113</v>
+        <v>1121</v>
       </c>
       <c r="B352" s="16" t="s">
-        <v>1114</v>
+        <v>1122</v>
       </c>
       <c r="C352" s="19"/>
     </row>
     <row r="353" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A353" s="17" t="s">
-        <v>1115</v>
+        <v>1123</v>
       </c>
       <c r="B353" s="16" t="s">
-        <v>1116</v>
+        <v>1124</v>
       </c>
       <c r="C353" s="19"/>
     </row>
     <row r="354" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A354" s="17" t="s">
-        <v>1117</v>
+        <v>1125</v>
       </c>
       <c r="B354" s="16" t="s">
-        <v>1118</v>
+        <v>1126</v>
       </c>
       <c r="C354" s="19"/>
     </row>
     <row r="355" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A355" s="17" t="s">
-        <v>1119</v>
+        <v>1127</v>
       </c>
       <c r="B355" s="16" t="s">
-        <v>1120</v>
+        <v>1128</v>
       </c>
       <c r="C355" s="19"/>
     </row>
     <row r="356" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A356" s="17" t="s">
-        <v>1121</v>
+        <v>1129</v>
       </c>
       <c r="B356" s="16" t="s">
-        <v>1122</v>
+        <v>1130</v>
       </c>
       <c r="C356" s="19"/>
     </row>
     <row r="360" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A360" s="24" t="s">
-        <v>1123</v>
-      </c>
-      <c r="B360" s="25"/>
-      <c r="C360" s="25"/>
+      <c r="A360" s="27" t="s">
+        <v>1131</v>
+      </c>
+      <c r="B360" s="28"/>
+      <c r="C360" s="28"/>
     </row>
     <row r="361" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A361" s="17" t="s">
-        <v>1124</v>
+        <v>1132</v>
       </c>
       <c r="B361" s="16" t="s">
-        <v>1125</v>
+        <v>1133</v>
       </c>
       <c r="C361" s="19"/>
     </row>
     <row r="362" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A362" s="17" t="s">
-        <v>1126</v>
+        <v>1134</v>
       </c>
       <c r="B362" s="16" t="s">
-        <v>1127</v>
+        <v>1135</v>
       </c>
       <c r="C362" s="19"/>
     </row>
     <row r="363" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A363" s="17" t="s">
-        <v>1128</v>
+        <v>1136</v>
       </c>
       <c r="B363" s="16" t="s">
-        <v>1129</v>
+        <v>1137</v>
       </c>
       <c r="C363" s="19"/>
     </row>
     <row r="364" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A364" s="17" t="s">
-        <v>1130</v>
+        <v>1138</v>
       </c>
       <c r="B364" s="16" t="s">
-        <v>1131</v>
+        <v>1139</v>
       </c>
       <c r="C364" s="19"/>
     </row>
     <row r="365" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A365" s="17" t="s">
-        <v>1132</v>
+        <v>1140</v>
       </c>
       <c r="B365" s="16" t="s">
-        <v>1133</v>
+        <v>1141</v>
       </c>
       <c r="C365" s="19"/>
     </row>
     <row r="366" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A366" s="17" t="s">
-        <v>1134</v>
+        <v>1142</v>
       </c>
       <c r="B366" s="16" t="s">
-        <v>1135</v>
+        <v>1143</v>
       </c>
       <c r="C366" s="19"/>
     </row>
     <row r="367" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A367" s="17" t="s">
-        <v>1136</v>
+        <v>1144</v>
       </c>
       <c r="B367" s="16" t="s">
-        <v>1137</v>
+        <v>1145</v>
       </c>
       <c r="C367" s="19"/>
     </row>
     <row r="369" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A369" s="24" t="s">
-        <v>1138</v>
-      </c>
-      <c r="B369" s="25"/>
-      <c r="C369" s="25"/>
+      <c r="A369" s="27" t="s">
+        <v>1146</v>
+      </c>
+      <c r="B369" s="28"/>
+      <c r="C369" s="28"/>
     </row>
     <row r="370" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A370" s="17" t="s">
-        <v>1139</v>
+        <v>1147</v>
       </c>
       <c r="B370" s="16" t="s">
-        <v>1140</v>
+        <v>1148</v>
       </c>
       <c r="C370" s="19"/>
     </row>
     <row r="371" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A371" s="17" t="s">
-        <v>1141</v>
+        <v>1149</v>
       </c>
       <c r="B371" s="16" t="s">
-        <v>1142</v>
+        <v>1150</v>
       </c>
       <c r="C371" s="19"/>
     </row>
     <row r="372" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A372" s="17" t="s">
-        <v>1143</v>
+        <v>1151</v>
       </c>
       <c r="B372" s="16" t="s">
-        <v>1144</v>
+        <v>1152</v>
       </c>
       <c r="C372" s="19"/>
     </row>
     <row r="373" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A373" s="24" t="s">
-        <v>1145</v>
-      </c>
-      <c r="B373" s="25"/>
-      <c r="C373" s="25"/>
+      <c r="A373" s="27" t="s">
+        <v>1153</v>
+      </c>
+      <c r="B373" s="28"/>
+      <c r="C373" s="28"/>
     </row>
     <row r="374" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A374" s="17" t="s">
-        <v>1146</v>
+        <v>1154</v>
       </c>
       <c r="B374" s="16" t="s">
-        <v>1147</v>
+        <v>1155</v>
       </c>
       <c r="C374" s="19"/>
     </row>
     <row r="375" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A375" s="17" t="s">
-        <v>1148</v>
+        <v>1156</v>
       </c>
       <c r="B375" s="16" t="s">
-        <v>1149</v>
+        <v>1157</v>
       </c>
       <c r="C375" s="19"/>
     </row>
     <row r="376" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A376" s="17" t="s">
-        <v>1150</v>
+        <v>1158</v>
       </c>
       <c r="B376" s="16" t="s">
-        <v>1151</v>
+        <v>1159</v>
       </c>
       <c r="C376" s="19"/>
     </row>
     <row r="377" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A377" s="24" t="s">
-        <v>1152</v>
-      </c>
-      <c r="B377" s="25"/>
-      <c r="C377" s="25"/>
+      <c r="A377" s="27" t="s">
+        <v>1160</v>
+      </c>
+      <c r="B377" s="28"/>
+      <c r="C377" s="28"/>
     </row>
     <row r="378" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A378" s="17" t="s">
-        <v>1153</v>
+        <v>1161</v>
       </c>
       <c r="B378" s="16" t="s">
-        <v>1154</v>
+        <v>1162</v>
       </c>
       <c r="C378" s="19"/>
     </row>
     <row r="379" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A379" s="17" t="s">
-        <v>1155</v>
+        <v>1163</v>
       </c>
       <c r="B379" s="16" t="s">
-        <v>1156</v>
+        <v>1164</v>
       </c>
       <c r="C379" s="19"/>
     </row>
     <row r="380" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A380" s="17" t="s">
-        <v>1157</v>
+        <v>1165</v>
       </c>
       <c r="B380" s="16" t="s">
-        <v>1158</v>
+        <v>1166</v>
       </c>
       <c r="C380" s="19"/>
     </row>
     <row r="381" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A381" s="24" t="s">
-        <v>1159</v>
-      </c>
-      <c r="B381" s="25"/>
-      <c r="C381" s="25"/>
+      <c r="A381" s="27" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B381" s="28"/>
+      <c r="C381" s="28"/>
     </row>
     <row r="382" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A382" s="17" t="s">
-        <v>1160</v>
+        <v>1168</v>
       </c>
       <c r="B382" s="16" t="s">
-        <v>1161</v>
+        <v>1169</v>
       </c>
       <c r="C382" s="19"/>
     </row>
     <row r="383" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A383" s="17" t="s">
-        <v>1162</v>
+        <v>1170</v>
       </c>
       <c r="B383" s="16" t="s">
-        <v>1163</v>
+        <v>1171</v>
       </c>
       <c r="C383" s="19"/>
     </row>
     <row r="384" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A384" s="24" t="s">
-        <v>1164</v>
-      </c>
-      <c r="B384" s="25"/>
-      <c r="C384" s="25"/>
+      <c r="A384" s="27" t="s">
+        <v>1172</v>
+      </c>
+      <c r="B384" s="28"/>
+      <c r="C384" s="28"/>
     </row>
     <row r="385" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A385" s="17" t="s">
-        <v>1165</v>
+        <v>1173</v>
       </c>
       <c r="B385" s="16" t="s">
-        <v>1166</v>
+        <v>1174</v>
       </c>
       <c r="C385" s="19"/>
     </row>
     <row r="386" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A386" s="17" t="s">
-        <v>1167</v>
+        <v>1175</v>
       </c>
       <c r="B386" s="16" t="s">
-        <v>1168</v>
+        <v>1176</v>
       </c>
       <c r="C386" s="19"/>
     </row>
     <row r="387" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A387" s="17" t="s">
-        <v>1169</v>
+        <v>1177</v>
       </c>
       <c r="B387" s="16" t="s">
-        <v>1170</v>
+        <v>1178</v>
       </c>
       <c r="C387" s="19"/>
     </row>
     <row r="388" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="389" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A389" s="24" t="s">
-        <v>1171</v>
-      </c>
-      <c r="B389" s="25"/>
-      <c r="C389" s="25"/>
+      <c r="A389" s="27" t="s">
+        <v>1179</v>
+      </c>
+      <c r="B389" s="28"/>
+      <c r="C389" s="28"/>
     </row>
     <row r="390" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A390" s="17" t="s">
-        <v>1172</v>
+        <v>1180</v>
       </c>
       <c r="B390" s="16" t="s">
-        <v>1173</v>
+        <v>1181</v>
       </c>
       <c r="C390" s="19"/>
     </row>
     <row r="391" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A391" s="17" t="s">
-        <v>1174</v>
+        <v>1182</v>
       </c>
       <c r="B391" s="16" t="s">
-        <v>1175</v>
+        <v>1183</v>
       </c>
       <c r="C391" s="19"/>
     </row>
     <row r="392" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A392" s="17" t="s">
-        <v>1176</v>
+        <v>1184</v>
       </c>
       <c r="B392" s="16" t="s">
-        <v>1177</v>
+        <v>1185</v>
       </c>
       <c r="C392" s="19"/>
     </row>
     <row r="393" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A393" s="17" t="s">
-        <v>1178</v>
+        <v>1186</v>
       </c>
       <c r="B393" s="16" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="C393" s="19"/>
     </row>
     <row r="394" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A394" s="26" t="s">
-        <v>1180</v>
-      </c>
-      <c r="B394" s="27"/>
-      <c r="C394" s="27"/>
+      <c r="A394" s="29" t="s">
+        <v>1188</v>
+      </c>
+      <c r="B394" s="30"/>
+      <c r="C394" s="30"/>
     </row>
     <row r="395" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A395" s="17" t="s">
-        <v>1181</v>
+        <v>1189</v>
       </c>
       <c r="B395" s="16" t="s">
-        <v>1182</v>
+        <v>1190</v>
       </c>
       <c r="C395" s="19"/>
     </row>
     <row r="396" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A396" s="17" t="s">
-        <v>1183</v>
+        <v>1191</v>
       </c>
       <c r="B396" s="16" t="s">
-        <v>1184</v>
+        <v>1192</v>
       </c>
       <c r="C396" s="19"/>
     </row>
     <row r="397" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A397" s="17" t="s">
-        <v>1185</v>
+        <v>1193</v>
       </c>
       <c r="B397" s="16" t="s">
-        <v>1186</v>
+        <v>1194</v>
       </c>
       <c r="C397" s="19"/>
     </row>
     <row r="398" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A398" s="17" t="s">
-        <v>1187</v>
+        <v>1195</v>
       </c>
       <c r="B398" s="16" t="s">
-        <v>1188</v>
+        <v>1196</v>
       </c>
       <c r="C398" s="19"/>
     </row>
     <row r="399" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A399" s="17" t="s">
-        <v>1189</v>
+        <v>1197</v>
       </c>
       <c r="B399" s="16" t="s">
-        <v>1190</v>
+        <v>1198</v>
       </c>
       <c r="C399" s="19"/>
     </row>
     <row r="400" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A400" s="26" t="s">
-        <v>1191</v>
-      </c>
-      <c r="B400" s="27"/>
-      <c r="C400" s="27"/>
+      <c r="A400" s="29" t="s">
+        <v>1199</v>
+      </c>
+      <c r="B400" s="30"/>
+      <c r="C400" s="30"/>
     </row>
     <row r="401" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A401" s="17" t="s">
-        <v>1192</v>
+        <v>1200</v>
       </c>
       <c r="B401" s="16" t="s">
-        <v>1193</v>
+        <v>1201</v>
       </c>
       <c r="C401" s="19"/>
     </row>
     <row r="402" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A402" s="17" t="s">
-        <v>1194</v>
+        <v>1202</v>
       </c>
       <c r="B402" s="16" t="s">
-        <v>1195</v>
+        <v>1203</v>
       </c>
       <c r="C402" s="19"/>
     </row>
     <row r="403" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A403" s="17" t="s">
-        <v>1196</v>
+        <v>1204</v>
       </c>
       <c r="B403" s="16" t="s">
-        <v>1197</v>
+        <v>1205</v>
       </c>
       <c r="C403" s="19"/>
     </row>
     <row r="404" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A404" s="17" t="s">
-        <v>1198</v>
+        <v>1206</v>
       </c>
       <c r="B404" s="16" t="s">
-        <v>1199</v>
+        <v>1207</v>
       </c>
       <c r="C404" s="19"/>
     </row>
     <row r="405" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A405" s="24" t="s">
-        <v>1200</v>
-      </c>
-      <c r="B405" s="25"/>
-      <c r="C405" s="25"/>
+      <c r="A405" s="27" t="s">
+        <v>1208</v>
+      </c>
+      <c r="B405" s="28"/>
+      <c r="C405" s="28"/>
     </row>
     <row r="406" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A406" s="17" t="s">
-        <v>1201</v>
+        <v>1209</v>
       </c>
       <c r="B406" s="16" t="s">
-        <v>1202</v>
+        <v>1210</v>
       </c>
       <c r="C406" s="19"/>
     </row>
     <row r="407" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A407" s="17" t="s">
-        <v>1203</v>
+        <v>1211</v>
       </c>
       <c r="B407" s="16" t="s">
-        <v>1204</v>
+        <v>1212</v>
       </c>
       <c r="C407" s="19"/>
     </row>
     <row r="408" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A408" s="17" t="s">
-        <v>1205</v>
+        <v>1213</v>
       </c>
       <c r="B408" s="16" t="s">
-        <v>1206</v>
+        <v>1214</v>
       </c>
       <c r="C408" s="19"/>
     </row>
     <row r="409" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A409" s="17" t="s">
-        <v>1207</v>
+        <v>1215</v>
       </c>
       <c r="B409" s="16" t="s">
-        <v>1208</v>
+        <v>1216</v>
       </c>
       <c r="C409" s="19"/>
     </row>
     <row r="410" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A410" s="26" t="s">
-        <v>1209</v>
-      </c>
-      <c r="B410" s="27"/>
-      <c r="C410" s="27"/>
+      <c r="A410" s="29" t="s">
+        <v>1217</v>
+      </c>
+      <c r="B410" s="30"/>
+      <c r="C410" s="30"/>
     </row>
     <row r="411" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A411" s="17" t="s">
-        <v>1210</v>
+        <v>1218</v>
       </c>
       <c r="B411" s="16" t="s">
-        <v>1211</v>
+        <v>1219</v>
       </c>
       <c r="C411" s="19"/>
     </row>
     <row r="412" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A412" s="17" t="s">
-        <v>1212</v>
+        <v>1220</v>
       </c>
       <c r="B412" s="16" t="s">
-        <v>1213</v>
+        <v>1221</v>
       </c>
       <c r="C412" s="19"/>
     </row>
     <row r="413" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A413" s="17" t="s">
-        <v>1214</v>
+        <v>1222</v>
       </c>
       <c r="B413" s="16" t="s">
-        <v>1215</v>
+        <v>1223</v>
       </c>
       <c r="C413" s="19"/>
     </row>
     <row r="414" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A414" s="17" t="s">
-        <v>1216</v>
+        <v>1224</v>
       </c>
       <c r="B414" s="16" t="s">
-        <v>1217</v>
+        <v>1225</v>
       </c>
       <c r="C414" s="19"/>
     </row>
     <row r="415" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A415" s="17" t="s">
-        <v>1218</v>
+        <v>1226</v>
       </c>
       <c r="B415" s="16" t="s">
-        <v>1219</v>
+        <v>1227</v>
       </c>
       <c r="C415" s="19"/>
     </row>
     <row r="416" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A416" s="26" t="s">
-        <v>1220</v>
-      </c>
-      <c r="B416" s="27"/>
-      <c r="C416" s="27"/>
+      <c r="A416" s="29" t="s">
+        <v>1228</v>
+      </c>
+      <c r="B416" s="30"/>
+      <c r="C416" s="30"/>
     </row>
     <row r="417" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A417" s="17" t="s">
-        <v>1221</v>
+        <v>1229</v>
       </c>
       <c r="B417" s="16" t="s">
-        <v>1222</v>
+        <v>1230</v>
       </c>
       <c r="C417" s="19"/>
     </row>
     <row r="418" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A418" s="17" t="s">
-        <v>1223</v>
+        <v>1231</v>
       </c>
       <c r="B418" s="16" t="s">
-        <v>1224</v>
+        <v>1232</v>
       </c>
       <c r="C418" s="19"/>
     </row>
     <row r="419" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A419" s="17" t="s">
-        <v>1225</v>
+        <v>1233</v>
       </c>
       <c r="B419" s="16" t="s">
-        <v>1226</v>
+        <v>1234</v>
       </c>
       <c r="C419" s="19"/>
     </row>
     <row r="420" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A420" s="17" t="s">
-        <v>1227</v>
+        <v>1235</v>
       </c>
       <c r="B420" s="16" t="s">
-        <v>1228</v>
+        <v>1236</v>
       </c>
       <c r="C420" s="19"/>
     </row>
     <row r="421" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A421" s="17" t="s">
-        <v>1229</v>
+        <v>1237</v>
       </c>
       <c r="B421" s="16" t="s">
-        <v>1230</v>
+        <v>1238</v>
       </c>
       <c r="C421" s="19"/>
     </row>
     <row r="422" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A422" s="24" t="s">
-        <v>1231</v>
-      </c>
-      <c r="B422" s="25"/>
-      <c r="C422" s="25"/>
+      <c r="A422" s="27" t="s">
+        <v>1239</v>
+      </c>
+      <c r="B422" s="28"/>
+      <c r="C422" s="28"/>
     </row>
     <row r="423" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A423" s="17" t="s">
-        <v>1232</v>
+        <v>1240</v>
       </c>
       <c r="B423" s="16" t="s">
-        <v>1233</v>
+        <v>1241</v>
       </c>
       <c r="C423" s="19"/>
     </row>
     <row r="424" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A424" s="17" t="s">
-        <v>1234</v>
+        <v>1242</v>
       </c>
       <c r="B424" s="16" t="s">
-        <v>1235</v>
+        <v>1243</v>
       </c>
       <c r="C424" s="19"/>
     </row>
     <row r="425" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A425" s="17" t="s">
-        <v>1236</v>
+        <v>1244</v>
       </c>
       <c r="B425" s="16" t="s">
-        <v>1237</v>
+        <v>1245</v>
       </c>
       <c r="C425" s="19"/>
     </row>
     <row r="426" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A426" s="24" t="s">
-        <v>1238</v>
-      </c>
-      <c r="B426" s="25"/>
-      <c r="C426" s="25"/>
+      <c r="A426" s="27" t="s">
+        <v>1246</v>
+      </c>
+      <c r="B426" s="28"/>
+      <c r="C426" s="28"/>
     </row>
     <row r="427" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A427" s="17" t="s">
-        <v>1239</v>
+        <v>1247</v>
       </c>
       <c r="B427" s="16" t="s">
-        <v>1240</v>
+        <v>1248</v>
       </c>
       <c r="C427" s="19"/>
     </row>
     <row r="428" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A428" s="17" t="s">
-        <v>1241</v>
+        <v>1249</v>
       </c>
       <c r="B428" s="16" t="s">
-        <v>1242</v>
+        <v>1250</v>
       </c>
       <c r="C428" s="19"/>
     </row>
     <row r="429" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A429" s="17" t="s">
-        <v>1243</v>
+        <v>1251</v>
       </c>
       <c r="B429" s="16" t="s">
-        <v>1244</v>
+        <v>1252</v>
       </c>
       <c r="C429" s="19"/>
     </row>
     <row r="430" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A430" s="24" t="s">
-        <v>1245</v>
-      </c>
-      <c r="B430" s="25"/>
-      <c r="C430" s="25"/>
+      <c r="A430" s="27" t="s">
+        <v>1253</v>
+      </c>
+      <c r="B430" s="28"/>
+      <c r="C430" s="28"/>
     </row>
     <row r="431" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A431" s="17" t="s">
-        <v>1246</v>
+        <v>1254</v>
       </c>
       <c r="B431" s="16" t="s">
-        <v>1247</v>
+        <v>1255</v>
       </c>
       <c r="C431" s="19"/>
     </row>
     <row r="432" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A432" s="17" t="s">
-        <v>1248</v>
+        <v>1256</v>
       </c>
       <c r="B432" s="16" t="s">
-        <v>1249</v>
+        <v>1257</v>
       </c>
       <c r="C432" s="19"/>
     </row>
     <row r="433" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A433" s="17" t="s">
-        <v>1250</v>
+        <v>1258</v>
       </c>
       <c r="B433" s="16" t="s">
-        <v>1251</v>
+        <v>1259</v>
       </c>
       <c r="C433" s="19"/>
     </row>
     <row r="434" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A434" s="17" t="s">
-        <v>1252</v>
+        <v>1260</v>
       </c>
       <c r="B434" s="16" t="s">
-        <v>1253</v>
+        <v>1261</v>
       </c>
       <c r="C434" s="19"/>
     </row>
     <row r="435" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A435" s="26" t="s">
-        <v>1254</v>
-      </c>
-      <c r="B435" s="27"/>
-      <c r="C435" s="27"/>
+      <c r="A435" s="29" t="s">
+        <v>1262</v>
+      </c>
+      <c r="B435" s="30"/>
+      <c r="C435" s="30"/>
     </row>
     <row r="436" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A436" s="17" t="s">
-        <v>1255</v>
+        <v>1263</v>
       </c>
       <c r="B436" s="16" t="s">
-        <v>1256</v>
+        <v>1264</v>
       </c>
       <c r="C436" s="19"/>
     </row>
     <row r="437" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A437" s="17" t="s">
-        <v>1257</v>
+        <v>1265</v>
       </c>
       <c r="B437" s="16" t="s">
-        <v>1258</v>
+        <v>1266</v>
       </c>
       <c r="C437" s="19"/>
     </row>
     <row r="438" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A438" s="17" t="s">
-        <v>1259</v>
+        <v>1267</v>
       </c>
       <c r="B438" s="16" t="s">
-        <v>1260</v>
+        <v>1268</v>
       </c>
       <c r="C438" s="19"/>
     </row>
     <row r="439" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A439" s="17" t="s">
-        <v>1261</v>
+        <v>1269</v>
       </c>
       <c r="B439" s="16" t="s">
-        <v>1262</v>
+        <v>1270</v>
       </c>
       <c r="C439" s="19"/>
     </row>
     <row r="440" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A440" s="17" t="s">
-        <v>1263</v>
+        <v>1271</v>
       </c>
       <c r="B440" s="16" t="s">
-        <v>1264</v>
+        <v>1272</v>
       </c>
       <c r="C440" s="19"/>
     </row>
     <row r="441" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A441" s="17" t="s">
-        <v>1265</v>
+        <v>1273</v>
       </c>
       <c r="B441" s="16" t="s">
-        <v>1266</v>
+        <v>1274</v>
       </c>
       <c r="C441" s="19"/>
     </row>
     <row r="443" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A443" s="24" t="s">
-        <v>1267</v>
-      </c>
-      <c r="B443" s="25"/>
-      <c r="C443" s="25"/>
+      <c r="A443" s="27" t="s">
+        <v>1275</v>
+      </c>
+      <c r="B443" s="28"/>
+      <c r="C443" s="28"/>
     </row>
     <row r="444" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A444" s="17" t="s">
-        <v>1268</v>
+        <v>1276</v>
       </c>
       <c r="B444" s="16" t="s">
-        <v>1269</v>
+        <v>1277</v>
       </c>
       <c r="C444" s="19"/>
     </row>
     <row r="445" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="446" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A446" s="24" t="s">
-        <v>1270</v>
-      </c>
-      <c r="B446" s="25"/>
-      <c r="C446" s="25"/>
+      <c r="A446" s="27" t="s">
+        <v>1278</v>
+      </c>
+      <c r="B446" s="28"/>
+      <c r="C446" s="28"/>
     </row>
     <row r="447" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A447" s="17" t="s">
-        <v>1271</v>
+        <v>1279</v>
       </c>
       <c r="B447" s="16" t="s">
-        <v>1272</v>
+        <v>1280</v>
       </c>
       <c r="C447" s="19"/>
     </row>
     <row r="448" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="449" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A449" s="26" t="s">
-        <v>1273</v>
-      </c>
-      <c r="B449" s="27"/>
-      <c r="C449" s="27"/>
+      <c r="A449" s="29" t="s">
+        <v>1281</v>
+      </c>
+      <c r="B449" s="30"/>
+      <c r="C449" s="30"/>
     </row>
     <row r="450" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A450" s="17" t="s">
-        <v>1274</v>
+        <v>1282</v>
       </c>
       <c r="B450" s="16" t="s">
-        <v>1275</v>
+        <v>1283</v>
       </c>
       <c r="C450" s="19"/>
     </row>
     <row r="451" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A451" s="17" t="s">
-        <v>1276</v>
+        <v>1284</v>
       </c>
       <c r="B451" s="16" t="s">
-        <v>1277</v>
+        <v>1285</v>
       </c>
       <c r="C451" s="19"/>
     </row>
     <row r="452" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A452" s="17" t="s">
-        <v>1278</v>
+        <v>1286</v>
       </c>
       <c r="B452" s="16" t="s">
-        <v>1279</v>
+        <v>1287</v>
       </c>
       <c r="C452" s="19"/>
     </row>
     <row r="453" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A453" s="17" t="s">
-        <v>1280</v>
+        <v>1288</v>
       </c>
       <c r="B453" s="16" t="s">
-        <v>1281</v>
+        <v>1289</v>
       </c>
       <c r="C453" s="19"/>
     </row>
     <row r="454" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A454" s="17" t="s">
-        <v>1282</v>
+        <v>1290</v>
       </c>
       <c r="B454" s="16" t="s">
-        <v>1283</v>
+        <v>1291</v>
       </c>
       <c r="C454" s="19"/>
     </row>
     <row r="455" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A455" s="17" t="s">
-        <v>1284</v>
+        <v>1292</v>
       </c>
       <c r="B455" s="16" t="s">
-        <v>1285</v>
+        <v>1293</v>
       </c>
       <c r="C455" s="19"/>
     </row>
     <row r="456" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A456" s="17" t="s">
-        <v>1286</v>
+        <v>1294</v>
       </c>
       <c r="B456" s="16" t="s">
-        <v>1287</v>
+        <v>1295</v>
       </c>
       <c r="C456" s="19"/>
     </row>
     <row r="457" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A457" s="24" t="s">
-        <v>1288</v>
-      </c>
-      <c r="B457" s="25"/>
-      <c r="C457" s="25"/>
+      <c r="A457" s="27" t="s">
+        <v>1296</v>
+      </c>
+      <c r="B457" s="28"/>
+      <c r="C457" s="28"/>
     </row>
     <row r="458" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A458" s="17" t="s">
-        <v>1289</v>
+        <v>1297</v>
       </c>
       <c r="B458" s="16" t="s">
-        <v>1290</v>
+        <v>1298</v>
       </c>
       <c r="C458" s="19"/>
     </row>
     <row r="459" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A459" s="17" t="s">
-        <v>1291</v>
+        <v>1299</v>
       </c>
       <c r="B459" s="16" t="s">
-        <v>1292</v>
+        <v>1300</v>
       </c>
       <c r="C459" s="19"/>
     </row>
     <row r="460" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A460" s="17" t="s">
-        <v>1293</v>
+        <v>1301</v>
       </c>
       <c r="B460" s="16" t="s">
-        <v>1294</v>
+        <v>1302</v>
       </c>
       <c r="C460" s="19"/>
     </row>
     <row r="461" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A461" s="28" t="s">
-        <v>1295</v>
-      </c>
-      <c r="B461" s="28"/>
-      <c r="C461" s="28"/>
+      <c r="A461" s="31" t="s">
+        <v>1303</v>
+      </c>
+      <c r="B461" s="31"/>
+      <c r="C461" s="31"/>
     </row>
     <row r="462" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A462" s="17" t="s">
-        <v>1296</v>
+        <v>1304</v>
       </c>
       <c r="B462" s="16" t="s">
-        <v>1297</v>
+        <v>1305</v>
       </c>
       <c r="C462" s="19"/>
     </row>
     <row r="463" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A463" s="17" t="s">
-        <v>1298</v>
+        <v>1306</v>
       </c>
       <c r="B463" s="16" t="s">
-        <v>1299</v>
+        <v>1307</v>
       </c>
       <c r="C463" s="19"/>
     </row>
     <row r="464" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A464" s="17" t="s">
-        <v>1300</v>
+        <v>1308</v>
       </c>
       <c r="B464" s="16" t="s">
-        <v>1301</v>
+        <v>1309</v>
       </c>
       <c r="C464" s="19"/>
     </row>
     <row r="465" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A465" s="17" t="s">
-        <v>1302</v>
+        <v>1310</v>
       </c>
       <c r="B465" s="16" t="s">
-        <v>1303</v>
+        <v>1311</v>
       </c>
       <c r="C465" s="19"/>
     </row>
     <row r="466" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A466" s="17" t="s">
-        <v>1304</v>
+        <v>1312</v>
       </c>
       <c r="B466" s="16" t="s">
-        <v>1305</v>
+        <v>1313</v>
       </c>
       <c r="C466" s="19"/>
     </row>
     <row r="467" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A467" s="17" t="s">
-        <v>1306</v>
+        <v>1314</v>
       </c>
       <c r="B467" s="16" t="s">
-        <v>1307</v>
+        <v>1315</v>
       </c>
       <c r="C467" s="19"/>
     </row>
-    <row r="468" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="468" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A468" s="17" t="s">
-        <v>1308</v>
+        <v>1316</v>
       </c>
       <c r="B468" s="16" t="s">
-        <v>1309</v>
+        <v>1317</v>
       </c>
       <c r="C468" s="19"/>
     </row>
-    <row r="470" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A470" s="24" t="s">
-        <v>1310</v>
-      </c>
-      <c r="B470" s="25"/>
-      <c r="C470" s="25"/>
-    </row>
-    <row r="471" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="470" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A470" s="27" t="s">
+        <v>1318</v>
+      </c>
+      <c r="B470" s="28"/>
+      <c r="C470" s="28"/>
+    </row>
+    <row r="471" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A471" s="17" t="s">
-        <v>1311</v>
+        <v>1319</v>
       </c>
       <c r="B471" s="16" t="s">
-        <v>1312</v>
-      </c>
-      <c r="C471" s="19" t="s">
-        <v>1313</v>
-      </c>
-    </row>
-    <row r="472" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1320</v>
+      </c>
+      <c r="C471" s="19"/>
+    </row>
+    <row r="472" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A472" s="17" t="s">
-        <v>1314</v>
+        <v>1321</v>
       </c>
       <c r="B472" s="16" t="s">
-        <v>1315</v>
+        <v>1322</v>
       </c>
       <c r="C472" s="19"/>
     </row>
-    <row r="473" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A473" s="17" t="s">
+    <row r="473" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A473" s="27" t="s">
+        <v>1323</v>
+      </c>
+      <c r="B473" s="28"/>
+      <c r="C473" s="28"/>
+    </row>
+    <row r="474" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A474" s="17" t="s">
+        <v>1324</v>
+      </c>
+      <c r="B474" s="16" t="s">
+        <v>1325</v>
+      </c>
+      <c r="C474" s="19"/>
+    </row>
+    <row r="475" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A475" s="17" t="s">
+        <v>1326</v>
+      </c>
+      <c r="B475" s="16" t="s">
+        <v>1327</v>
+      </c>
+      <c r="C475" s="19"/>
+    </row>
+    <row r="476" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A476" s="17" t="s">
+        <v>1328</v>
+      </c>
+      <c r="B476" s="16" t="s">
+        <v>1329</v>
+      </c>
+      <c r="C476" s="19"/>
+    </row>
+    <row r="477" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A477" s="29" t="s">
+        <v>1330</v>
+      </c>
+      <c r="B477" s="30"/>
+      <c r="C477" s="30"/>
+    </row>
+    <row r="478" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A478" s="17" t="s">
+        <v>1331</v>
+      </c>
+      <c r="B478" s="16" t="s">
+        <v>1332</v>
+      </c>
+      <c r="C478" s="19"/>
+    </row>
+    <row r="479" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A479" s="17" t="s">
+        <v>1333</v>
+      </c>
+      <c r="B479" s="16" t="s">
+        <v>1334</v>
+      </c>
+      <c r="C479" s="19"/>
+    </row>
+    <row r="480" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A480" s="17" t="s">
+        <v>1335</v>
+      </c>
+      <c r="B480" s="16" t="s">
+        <v>1336</v>
+      </c>
+      <c r="C480" s="19"/>
+    </row>
+    <row r="481" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A481" s="17" t="s">
+        <v>1337</v>
+      </c>
+      <c r="B481" s="16" t="s">
+        <v>1338</v>
+      </c>
+      <c r="C481" s="19"/>
+    </row>
+    <row r="482" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="483" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A483" s="31" t="s">
+        <v>1339</v>
+      </c>
+      <c r="B483" s="31"/>
+      <c r="C483" s="31"/>
+    </row>
+    <row r="484" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A484" s="17" t="s">
+        <v>1340</v>
+      </c>
+      <c r="B484" s="16" t="s">
+        <v>1341</v>
+      </c>
+      <c r="C484" s="19"/>
+    </row>
+    <row r="485" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A485" s="17" t="s">
+        <v>1342</v>
+      </c>
+      <c r="B485" s="16" t="s">
+        <v>1343</v>
+      </c>
+      <c r="C485" s="19"/>
+    </row>
+    <row r="486" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A486" s="17" t="s">
+        <v>1344</v>
+      </c>
+      <c r="B486" s="16" t="s">
+        <v>1345</v>
+      </c>
+      <c r="C486" s="19"/>
+    </row>
+    <row r="487" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A487" s="17" t="s">
+        <v>1346</v>
+      </c>
+      <c r="B487" s="16" t="s">
+        <v>1347</v>
+      </c>
+      <c r="C487" s="19"/>
+    </row>
+    <row r="488" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A488" s="17" t="s">
+        <v>1348</v>
+      </c>
+      <c r="B488" s="16" t="s">
+        <v>1349</v>
+      </c>
+      <c r="C488" s="19"/>
+    </row>
+    <row r="489" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A489" s="17" t="s">
+        <v>1350</v>
+      </c>
+      <c r="B489" s="16" t="s">
+        <v>1351</v>
+      </c>
+      <c r="C489" s="19"/>
+    </row>
+    <row r="490" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A490" s="17" t="s">
+        <v>1352</v>
+      </c>
+      <c r="B490" s="16" t="s">
+        <v>1353</v>
+      </c>
+      <c r="C490" s="19"/>
+    </row>
+    <row r="492" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A492" s="32" t="s">
+        <v>1354</v>
+      </c>
+      <c r="B492" s="32"/>
+      <c r="C492" s="32"/>
+    </row>
+    <row r="493" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A493" s="17" t="s">
+        <v>1355</v>
+      </c>
+      <c r="B493" s="16" t="s">
+        <v>1356</v>
+      </c>
+      <c r="C493" s="19"/>
+    </row>
+    <row r="494" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A494" s="17" t="s">
+        <v>1357</v>
+      </c>
+      <c r="B494" s="16" t="s">
+        <v>1358</v>
+      </c>
+      <c r="C494" s="19"/>
+    </row>
+    <row r="495" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A495" s="17" t="s">
+        <v>1359</v>
+      </c>
+      <c r="B495" s="16" t="s">
+        <v>1360</v>
+      </c>
+      <c r="C495" s="19"/>
+    </row>
+    <row r="496" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A496" s="17" t="s">
+        <v>1361</v>
+      </c>
+      <c r="B496" s="16" t="s">
+        <v>1362</v>
+      </c>
+      <c r="C496" s="19"/>
+    </row>
+    <row r="497" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A497" s="17" t="s">
+        <v>1363</v>
+      </c>
+      <c r="B497" s="16" t="s">
+        <v>1364</v>
+      </c>
+      <c r="C497" s="19"/>
+    </row>
+    <row r="498" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A498" s="27" t="s">
+        <v>1365</v>
+      </c>
+      <c r="B498" s="28"/>
+      <c r="C498" s="28"/>
+    </row>
+    <row r="499" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A499" s="17" t="s">
+        <v>1366</v>
+      </c>
+      <c r="B499" s="16" t="s">
+        <v>1367</v>
+      </c>
+      <c r="C499" s="19" t="s">
+        <v>1368</v>
+      </c>
+    </row>
+    <row r="500" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A500" s="17" t="s">
+        <v>1369</v>
+      </c>
+      <c r="B500" s="16" t="s">
+        <v>1370</v>
+      </c>
+      <c r="C500" s="19"/>
+    </row>
+    <row r="501" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A501" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="B473" s="16" t="s">
-        <v>1316</v>
-      </c>
-      <c r="C473" s="19" t="s">
-        <v>1317</v>
-      </c>
-    </row>
-    <row r="474" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A474" s="17" t="s">
-        <v>1318</v>
-      </c>
-      <c r="B474" s="16" t="s">
-        <v>1319</v>
-      </c>
-      <c r="C474" s="19"/>
-    </row>
-    <row r="475" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A475" s="17" t="s">
-        <v>1320</v>
-      </c>
-      <c r="B475" s="16" t="s">
-        <v>1321</v>
-      </c>
-      <c r="C475" s="19" t="s">
-        <v>1322</v>
-      </c>
-    </row>
-    <row r="476" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A476" s="17" t="s">
-        <v>1323</v>
-      </c>
-      <c r="B476" s="16" t="s">
-        <v>1324</v>
-      </c>
-      <c r="C476" s="19"/>
+      <c r="B501" s="16" t="s">
+        <v>1371</v>
+      </c>
+      <c r="C501" s="19" t="s">
+        <v>1372</v>
+      </c>
+    </row>
+    <row r="502" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A502" s="17" t="s">
+        <v>1373</v>
+      </c>
+      <c r="B502" s="16" t="s">
+        <v>1374</v>
+      </c>
+      <c r="C502" s="19"/>
+    </row>
+    <row r="503" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A503" s="17" t="s">
+        <v>1375</v>
+      </c>
+      <c r="B503" s="16" t="s">
+        <v>1376</v>
+      </c>
+      <c r="C503" s="19" t="s">
+        <v>1377</v>
+      </c>
+    </row>
+    <row r="504" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A504" s="17" t="s">
+        <v>1378</v>
+      </c>
+      <c r="B504" s="16" t="s">
+        <v>1379</v>
+      </c>
+      <c r="C504" s="19"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/umc-bck-complete/documents/UMC_BCK_Migration_Tracker.xlsx
+++ b/umc-bck-complete/documents/UMC_BCK_Migration_Tracker.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2836" uniqueCount="2050">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2874" uniqueCount="2087">
   <si>
     <t xml:space="preserve">UMC-BCK — Feature Migration Tracker</t>
   </si>
@@ -6133,6 +6133,117 @@
   </si>
   <si>
     <t xml:space="preserve">Full safety re-verification given the scale — real headless browser test and complete ESLint audit, both clean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CRITICAL — two real, precise bugs found and fixed. Both database-only, already live, no redeploy needed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Real, foundational bug found: the real signup trigger created a profile but never created a wallet — every single account, including the admin's own, had no wallet at all</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confirmed directly: 2 real users, 0 wallets, before this fix. Fixed the trigger to create a real wallet the moment any account is created, and backfilled wallets for the 2 real accounts that already existed. Verified: 2 users, 2 wallets, after the fix</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Real, precise bug found for the cart badge not updating: cart_items was never added to Supabase's real-time publication</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The insert logic and the subscription code were both already completely correct — checked line by line. The real, single missing piece was a database-level registration that tells Supabase to actually broadcast changes on this table at all. Fixed and verified directly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Both fixes are pure database changes — already live immediately, no new zip or redeploy required for either one</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kasuwa Price Watch restored — real bug found: it existed but was mislabeled 'My List', invisible in practice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Real bug found: the page genuinely existed and was correctly routed, but the bottom navigation link pointing to it was mislabeled 'My List' — nothing about that name would ever suggest price tracking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fixed the label to 'Price Watch', matching what it actually is</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What existed before was a different, narrower feature — a personal watch list requiring the user to manually add items first, empty until they did. Confirmed by reading the actual code, not assumed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kept this as a real, secondary section at the bottom of the new page — genuinely still useful, just not the main feature</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The real, original Kasuwa Price Watch rebuilt properly — platform-wide, live, real data throughout</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Real min/average/max price and real seller count per commodity, computed live from actual current listings — not fabricated numbers. Real week-over-week trend where genuine price history exists; shows 'New — not enough history yet' honestly where it doesn't, rather than a fake percentage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Real scrolling ticker banner restored, real category filters (All/Grains/Oils/Fresh/Household), real expandable detail cards showing lowest/average/highest with the real seller name for each</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matches the original design directly, verified against the real handover source</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Real, separate bug fixed in the same round: the Canteen hub's navigation label was just 'Canteen', missing 'Fast Food' — the actual Canteen page itself already had the correct full title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fixed the navigation label to match</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Full safety verification repeated given the scope — real headless browser test and complete ESLint audit, both clean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Canteen real screenshots implemented — architecture fix, 2 more menus, 2 missing platform-wide features found and built</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Real architectural fix: Nigerian Meals item choice and swallow choice were both meant to be single-select, but only one dimension can be a real product variant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Item choice (jollof/fried rice/white rice/beans/moi-moi/akara) moved to real variants. Swallow moved to its own real addon group, now correctly rendered as radio buttons, not checkboxes. Fast Food and Shawarma's size groups fixed the same way — they were wrongly multi-select before</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Northern Dishes and Drinks &amp; Beverages built as real menus, exact items and prices as given</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Northern Dishes: Tuwo shinkafa, Tuwo masara, Dan wake, Masa, Fura da nono, Dambu nama. Drinks: Fresh orange juice, Chapman, Zobo, Kunu, Smoothies, Milkshake, Malt, Water, Soft drink (can/PET), Energy drinks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Real, platform-wide 'Add to Market List' button found completely missing — confirmed the real database table existed but no button anywhere used it</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Built the real red circular tap target on every product card across the whole marketplace, not just canteen — matching the exact described behavior, save now, recall and check for price updates later</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Real five-tab Canteen structure rebuilt — List canteen, Incoming orders, Order food, Group order, Track — with the active tab genuinely bold, matching the original exactly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Previously only had category filters with no real top-level tab structure at all</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Honest, still-open piece: the real, uniform canteen-specific delivery zone and urgency system (Zone 1–4, Standard/Express/Priority/Night) has not been built yet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This is real, substantial work on its own — queued for the next round rather than rushed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The real, uniform canteen delivery zone and urgency system — closed out, the last open item from last round</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Real, dedicated database tables built for zones and urgency tiers — exact fees as given, editable by admin later without needing a new deploy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 real zones (₦700/₦1,200/₦1,800/₦2,500) and 4 real urgency tiers (Standard/Express/Priority/Night, exact surcharges) — confirmed uniform across all 8 canteen categories</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Real, dedicated Canteen Checkout page built — number of people eating, delivery method, zone selector, urgency selector, real live order breakdown</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reuses the same proven, already-tested place_order function underneath — not a new, unproven payment path — just real canteen-specific fee calculation feeding into it</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Real routing fix: canteen products now correctly lead to this dedicated checkout instead of the general marketplace cart</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Button itself changes to 'Build your order →' for real canteen items specifically, so it's clear before tapping that this is a different real flow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Full safety verification given this is a new checkout path — real headless browser test and complete ESLint audit, both clean</t>
   </si>
   <si>
     <t xml:space="preserve">NOT YET STARTED</t>
@@ -12712,7 +12823,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C918"/>
+  <dimension ref="A1:C952"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="30"/>
@@ -19294,11 +19405,11 @@
       <c r="C898" s="31"/>
     </row>
     <row r="903" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A903" s="47" t="s">
+      <c r="A903" s="46" t="s">
         <v>2025</v>
       </c>
-      <c r="B903" s="47"/>
-      <c r="C903" s="47"/>
+      <c r="B903" s="46"/>
+      <c r="C903" s="46"/>
     </row>
     <row r="904" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A904" s="16" t="s">
@@ -19344,72 +19455,268 @@
       <c r="C908" s="31"/>
     </row>
     <row r="909" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="912" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A912" s="41" t="s">
+    <row r="912" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A912" s="45" t="s">
         <v>2035</v>
       </c>
-      <c r="B912" s="42"/>
-      <c r="C912" s="42"/>
-    </row>
-    <row r="913" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B912" s="45"/>
+      <c r="C912" s="45"/>
+    </row>
+    <row r="913" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A913" s="16" t="s">
         <v>2036</v>
       </c>
       <c r="B913" s="17" t="s">
         <v>2037</v>
       </c>
-      <c r="C913" s="31" t="s">
+      <c r="C913" s="31"/>
+    </row>
+    <row r="914" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A914" s="16" t="s">
         <v>2038</v>
       </c>
-    </row>
-    <row r="914" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A914" s="16" t="s">
+      <c r="B914" s="17" t="s">
         <v>2039</v>
       </c>
-      <c r="B914" s="17" t="s">
+      <c r="C914" s="31"/>
+    </row>
+    <row r="915" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A915" s="16" t="s">
         <v>2040</v>
       </c>
-      <c r="C914" s="31"/>
-    </row>
-    <row r="915" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A915" s="16" t="s">
+      <c r="B915" s="17"/>
+      <c r="C915" s="31"/>
+    </row>
+    <row r="916" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="917" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="918" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="920" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A920" s="46" t="s">
+        <v>2041</v>
+      </c>
+      <c r="B920" s="46"/>
+      <c r="C920" s="46"/>
+    </row>
+    <row r="921" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A921" s="16" t="s">
+        <v>2042</v>
+      </c>
+      <c r="B921" s="17" t="s">
+        <v>2043</v>
+      </c>
+      <c r="C921" s="31"/>
+    </row>
+    <row r="922" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A922" s="16" t="s">
+        <v>2044</v>
+      </c>
+      <c r="B922" s="17" t="s">
+        <v>2045</v>
+      </c>
+      <c r="C922" s="31"/>
+    </row>
+    <row r="923" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A923" s="16" t="s">
+        <v>2046</v>
+      </c>
+      <c r="B923" s="17" t="s">
+        <v>2047</v>
+      </c>
+      <c r="C923" s="31"/>
+    </row>
+    <row r="924" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A924" s="16" t="s">
+        <v>2048</v>
+      </c>
+      <c r="B924" s="17" t="s">
+        <v>2049</v>
+      </c>
+      <c r="C924" s="31"/>
+    </row>
+    <row r="925" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A925" s="16" t="s">
+        <v>2050</v>
+      </c>
+      <c r="B925" s="17" t="s">
+        <v>2051</v>
+      </c>
+      <c r="C925" s="31"/>
+    </row>
+    <row r="926" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A926" s="16" t="s">
+        <v>2052</v>
+      </c>
+      <c r="B926" s="17"/>
+      <c r="C926" s="31"/>
+    </row>
+    <row r="929" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A929" s="46" t="s">
+        <v>2053</v>
+      </c>
+      <c r="B929" s="46"/>
+      <c r="C929" s="46"/>
+    </row>
+    <row r="930" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A930" s="16" t="s">
+        <v>2054</v>
+      </c>
+      <c r="B930" s="17" t="s">
+        <v>2055</v>
+      </c>
+      <c r="C930" s="31"/>
+    </row>
+    <row r="931" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A931" s="16" t="s">
+        <v>2056</v>
+      </c>
+      <c r="B931" s="17" t="s">
+        <v>2057</v>
+      </c>
+      <c r="C931" s="31"/>
+    </row>
+    <row r="932" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A932" s="16" t="s">
+        <v>2058</v>
+      </c>
+      <c r="B932" s="17" t="s">
+        <v>2059</v>
+      </c>
+      <c r="C932" s="31"/>
+    </row>
+    <row r="933" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A933" s="16" t="s">
+        <v>2060</v>
+      </c>
+      <c r="B933" s="17" t="s">
+        <v>2061</v>
+      </c>
+      <c r="C933" s="31"/>
+    </row>
+    <row r="934" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A934" s="16" t="s">
+        <v>2062</v>
+      </c>
+      <c r="B934" s="17" t="s">
+        <v>2063</v>
+      </c>
+      <c r="C934" s="31"/>
+    </row>
+    <row r="935" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A935" s="16" t="s">
+        <v>2052</v>
+      </c>
+      <c r="B935" s="17"/>
+      <c r="C935" s="31"/>
+    </row>
+    <row r="939" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A939" s="47" t="s">
+        <v>2064</v>
+      </c>
+      <c r="B939" s="47"/>
+      <c r="C939" s="47"/>
+    </row>
+    <row r="940" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A940" s="16" t="s">
+        <v>2065</v>
+      </c>
+      <c r="B940" s="17" t="s">
+        <v>2066</v>
+      </c>
+      <c r="C940" s="31"/>
+    </row>
+    <row r="941" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A941" s="16" t="s">
+        <v>2067</v>
+      </c>
+      <c r="B941" s="17" t="s">
+        <v>2068</v>
+      </c>
+      <c r="C941" s="31"/>
+    </row>
+    <row r="942" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A942" s="16" t="s">
+        <v>2069</v>
+      </c>
+      <c r="B942" s="17" t="s">
+        <v>2070</v>
+      </c>
+      <c r="C942" s="31"/>
+    </row>
+    <row r="943" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A943" s="16" t="s">
+        <v>2071</v>
+      </c>
+      <c r="B943" s="17"/>
+      <c r="C943" s="31"/>
+    </row>
+    <row r="944" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="945" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="946" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A946" s="41" t="s">
+        <v>2072</v>
+      </c>
+      <c r="B946" s="42"/>
+      <c r="C946" s="42"/>
+    </row>
+    <row r="947" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A947" s="16" t="s">
+        <v>2073</v>
+      </c>
+      <c r="B947" s="17" t="s">
+        <v>2074</v>
+      </c>
+      <c r="C947" s="31" t="s">
+        <v>2075</v>
+      </c>
+    </row>
+    <row r="948" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A948" s="16" t="s">
+        <v>2076</v>
+      </c>
+      <c r="B948" s="17" t="s">
+        <v>2077</v>
+      </c>
+      <c r="C948" s="31"/>
+    </row>
+    <row r="949" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A949" s="16" t="s">
         <v>163</v>
       </c>
-      <c r="B915" s="17" t="s">
-        <v>2041</v>
-      </c>
-      <c r="C915" s="31" t="s">
-        <v>2042</v>
-      </c>
-    </row>
-    <row r="916" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A916" s="16" t="s">
-        <v>2043</v>
-      </c>
-      <c r="B916" s="17" t="s">
-        <v>2044</v>
-      </c>
-      <c r="C916" s="31"/>
-    </row>
-    <row r="917" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A917" s="16" t="s">
-        <v>2045</v>
-      </c>
-      <c r="B917" s="17" t="s">
-        <v>2046</v>
-      </c>
-      <c r="C917" s="31" t="s">
-        <v>2047</v>
-      </c>
-    </row>
-    <row r="918" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A918" s="16" t="s">
-        <v>2048</v>
-      </c>
-      <c r="B918" s="17" t="s">
-        <v>2049</v>
-      </c>
-      <c r="C918" s="31"/>
+      <c r="B949" s="17" t="s">
+        <v>2078</v>
+      </c>
+      <c r="C949" s="31" t="s">
+        <v>2079</v>
+      </c>
+    </row>
+    <row r="950" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A950" s="16" t="s">
+        <v>2080</v>
+      </c>
+      <c r="B950" s="17" t="s">
+        <v>2081</v>
+      </c>
+      <c r="C950" s="31"/>
+    </row>
+    <row r="951" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A951" s="16" t="s">
+        <v>2082</v>
+      </c>
+      <c r="B951" s="17" t="s">
+        <v>2083</v>
+      </c>
+      <c r="C951" s="31" t="s">
+        <v>2084</v>
+      </c>
+    </row>
+    <row r="952" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A952" s="16" t="s">
+        <v>2085</v>
+      </c>
+      <c r="B952" s="17" t="s">
+        <v>2086</v>
+      </c>
+      <c r="C952" s="31"/>
     </row>
   </sheetData>
   <mergeCells count="2">
